--- a/portfolio_repo/assets/tc/inZOI_tc/inZOI_tc.xlsx
+++ b/portfolio_repo/assets/tc/inZOI_tc/inZOI_tc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hamincheol/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\master\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1333C72-983A-4545-9DAF-43E4E7D47DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D3528E-B3B6-493F-A353-2B8DE9C4C791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inZOI_Overview" sheetId="3" r:id="rId1"/>
@@ -4831,20 +4831,107 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="31" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="31" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -4875,132 +4962,47 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="30" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="31" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="31" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="2" xr:uid="{8829CE88-5FEC-4FDF-8B73-596F32B2351D}"/>
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="4">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b/>
+        <color rgb="FFFECACA"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF7F1D1D"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <b/>
+        <color rgb="FFBBF7D0"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF14532D"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5021,109 +5023,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.14996795556505021"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1" tint="0.14996795556505021"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFECACA"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF7F1D1D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFBBF7D0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF14532D"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5333,10 +5232,9 @@
     <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
+    <a:noFill/>
     <a:ln w="9525">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
+      <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
   </c:spPr>
@@ -5369,7 +5267,11 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:rPr>
               <a:t>Case Result Distribution</a:t>
             </a:r>
           </a:p>
@@ -5465,6 +5367,20 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="48672768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -5503,10 +5419,9 @@
     <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
+    <a:noFill/>
     <a:ln w="9525">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
+      <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
   </c:spPr>
@@ -7208,9 +7123,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>640896</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1361</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5810250" cy="2381250"/>
     <xdr:graphicFrame macro="">
@@ -7240,12 +7155,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>434067</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>204106</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4953000" cy="2095500"/>
+    <xdr:ext cx="4257675" cy="1743075"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart">
@@ -7279,6 +7194,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="inZOI_Overview"/>
@@ -9210,165 +9126,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DCC0EA7-7C51-1D4B-86DC-3B697246D466}">
   <dimension ref="A1:AD95"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:30" ht="15" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="80" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="52"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="81"/>
+      <c r="Z1" s="81"/>
       <c r="AA1" s="13"/>
       <c r="AB1" s="13"/>
       <c r="AC1" s="13"/>
       <c r="AD1" s="13"/>
     </row>
     <row r="2" spans="1:30" ht="15" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
-      <c r="Z2" s="52"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
+      <c r="Z2" s="81"/>
       <c r="AA2" s="13"/>
       <c r="AB2" s="13"/>
       <c r="AC2" s="13"/>
       <c r="AD2" s="13"/>
     </row>
     <row r="3" spans="1:30" ht="15" customHeight="1">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
-      <c r="Z3" s="52"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="81"/>
+      <c r="Y3" s="81"/>
+      <c r="Z3" s="81"/>
       <c r="AA3" s="13"/>
       <c r="AB3" s="13"/>
       <c r="AC3" s="13"/>
       <c r="AD3" s="13"/>
     </row>
     <row r="4" spans="1:30" ht="15" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="52"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="81"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="81"/>
+      <c r="U4" s="81"/>
+      <c r="V4" s="81"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="81"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
       <c r="AA4" s="13"/>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
       <c r="AD4" s="13"/>
     </row>
     <row r="5" spans="1:30" ht="15" customHeight="1">
-      <c r="A5" s="52"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="52"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="52"/>
-      <c r="Y5" s="52"/>
-      <c r="Z5" s="52"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="81"/>
+      <c r="O5" s="81"/>
+      <c r="P5" s="81"/>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="81"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="81"/>
+      <c r="U5" s="81"/>
+      <c r="V5" s="81"/>
+      <c r="W5" s="81"/>
+      <c r="X5" s="81"/>
+      <c r="Y5" s="81"/>
+      <c r="Z5" s="81"/>
       <c r="AA5" s="13"/>
       <c r="AB5" s="13"/>
       <c r="AC5" s="13"/>
@@ -12266,75 +12182,75 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R203"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="55.83203125" customWidth="1"/>
+    <col min="7" max="7" width="55.85546875" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="12" style="1" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="39.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="21.1640625" customWidth="1"/>
-    <col min="13" max="13" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="39.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.140625" customWidth="1"/>
+    <col min="13" max="13" width="21.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="33.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22" customHeight="1">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:18" ht="21.95" customHeight="1">
+      <c r="A1" s="82" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="56"/>
-    </row>
-    <row r="2" spans="1:18" ht="22" customHeight="1">
-      <c r="A2" s="61" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="84"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="85"/>
+    </row>
+    <row r="2" spans="1:18" ht="21.95" customHeight="1">
+      <c r="A2" s="90" t="s">
         <v>406</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="60"/>
-    </row>
-    <row r="3" spans="1:18" ht="22" customHeight="1">
-      <c r="A3" s="57" t="s">
+      <c r="B2" s="87"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="89"/>
+    </row>
+    <row r="3" spans="1:18" ht="21.95" customHeight="1">
+      <c r="A3" s="86" t="s">
         <v>404</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="58"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="87"/>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
       <c r="L3" s="10"/>
@@ -12342,7 +12258,7 @@
       <c r="N3" s="12"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:18" ht="34" customHeight="1">
+    <row r="4" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="24" t="s">
         <v>200</v>
       </c>
@@ -12389,7 +12305,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="34" customHeight="1">
+    <row r="5" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>21</v>
       </c>
@@ -12434,7 +12350,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="34" customHeight="1">
+    <row r="6" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="14" t="s">
         <v>21</v>
       </c>
@@ -12480,7 +12396,7 @@
       </c>
       <c r="Q6" s="6"/>
     </row>
-    <row r="7" spans="1:18" ht="34" customHeight="1">
+    <row r="7" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A7" s="14" t="s">
         <v>21</v>
       </c>
@@ -12526,7 +12442,7 @@
       </c>
       <c r="Q7" s="6"/>
     </row>
-    <row r="8" spans="1:18" ht="34" customHeight="1">
+    <row r="8" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="14" t="s">
         <v>21</v>
       </c>
@@ -12572,7 +12488,7 @@
       </c>
       <c r="Q8" s="6"/>
     </row>
-    <row r="9" spans="1:18" ht="34" customHeight="1">
+    <row r="9" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>21</v>
       </c>
@@ -12618,7 +12534,7 @@
       </c>
       <c r="Q9" s="6"/>
     </row>
-    <row r="10" spans="1:18" ht="34" customHeight="1">
+    <row r="10" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A10" s="14" t="s">
         <v>21</v>
       </c>
@@ -12664,7 +12580,7 @@
       </c>
       <c r="Q10" s="6"/>
     </row>
-    <row r="11" spans="1:18" ht="34" customHeight="1">
+    <row r="11" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A11" s="14" t="s">
         <v>21</v>
       </c>
@@ -12710,7 +12626,7 @@
       </c>
       <c r="Q11" s="6"/>
     </row>
-    <row r="12" spans="1:18" ht="34" customHeight="1">
+    <row r="12" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A12" s="14" t="s">
         <v>21</v>
       </c>
@@ -12756,7 +12672,7 @@
       </c>
       <c r="Q12" s="6"/>
     </row>
-    <row r="13" spans="1:18" ht="34" customHeight="1">
+    <row r="13" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A13" s="14" t="s">
         <v>21</v>
       </c>
@@ -12802,7 +12718,7 @@
       </c>
       <c r="Q13" s="6"/>
     </row>
-    <row r="14" spans="1:18" ht="34" customHeight="1">
+    <row r="14" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A14" s="14" t="s">
         <v>21</v>
       </c>
@@ -12848,7 +12764,7 @@
       </c>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:18" ht="34" customHeight="1">
+    <row r="15" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A15" s="14" t="s">
         <v>21</v>
       </c>
@@ -12893,7 +12809,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="34" customHeight="1">
+    <row r="16" spans="1:18" ht="33.950000000000003" customHeight="1">
       <c r="A16" s="14" t="s">
         <v>21</v>
       </c>
@@ -12939,7 +12855,7 @@
       </c>
       <c r="R16" s="6"/>
     </row>
-    <row r="17" spans="1:17" ht="34" customHeight="1">
+    <row r="17" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A17" s="14" t="s">
         <v>21</v>
       </c>
@@ -12984,7 +12900,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="34" customHeight="1">
+    <row r="18" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A18" s="14" t="s">
         <v>21</v>
       </c>
@@ -13029,7 +12945,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="34" customHeight="1">
+    <row r="19" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A19" s="14" t="s">
         <v>21</v>
       </c>
@@ -13075,7 +12991,7 @@
       </c>
       <c r="Q19" s="6"/>
     </row>
-    <row r="20" spans="1:17" ht="34" customHeight="1">
+    <row r="20" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A20" s="17"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -13093,7 +13009,7 @@
       <c r="O20" s="22"/>
       <c r="Q20" s="6"/>
     </row>
-    <row r="21" spans="1:17" ht="34" customHeight="1">
+    <row r="21" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A21" s="17"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -13111,7 +13027,7 @@
       <c r="O21" s="21"/>
       <c r="Q21" s="6"/>
     </row>
-    <row r="22" spans="1:17" ht="34" customHeight="1">
+    <row r="22" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A22" s="17"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -13129,7 +13045,7 @@
       <c r="O22" s="21"/>
       <c r="Q22" s="6"/>
     </row>
-    <row r="23" spans="1:17" ht="34" customHeight="1">
+    <row r="23" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A23" s="17"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -13146,7 +13062,7 @@
       <c r="N23" s="18"/>
       <c r="O23" s="21"/>
     </row>
-    <row r="24" spans="1:17" ht="34" customHeight="1">
+    <row r="24" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A24" s="17"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -13163,7 +13079,7 @@
       <c r="N24" s="18"/>
       <c r="O24" s="22"/>
     </row>
-    <row r="25" spans="1:17" ht="34" customHeight="1">
+    <row r="25" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A25" s="17"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -13180,7 +13096,7 @@
       <c r="N25" s="18"/>
       <c r="O25" s="22"/>
     </row>
-    <row r="26" spans="1:17" ht="34" customHeight="1">
+    <row r="26" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A26" s="17"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -13197,7 +13113,7 @@
       <c r="N26" s="18"/>
       <c r="O26" s="22"/>
     </row>
-    <row r="27" spans="1:17" ht="34" customHeight="1">
+    <row r="27" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A27" s="17"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -13214,7 +13130,7 @@
       <c r="N27" s="18"/>
       <c r="O27" s="22"/>
     </row>
-    <row r="28" spans="1:17" ht="34" customHeight="1">
+    <row r="28" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A28" s="31"/>
       <c r="B28" s="32"/>
       <c r="C28" s="32"/>
@@ -13231,7 +13147,7 @@
       <c r="N28" s="32"/>
       <c r="O28" s="34"/>
     </row>
-    <row r="29" spans="1:17" ht="34" customHeight="1">
+    <row r="29" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A29" s="35"/>
       <c r="B29" s="35"/>
       <c r="C29" s="35"/>
@@ -13248,7 +13164,7 @@
       <c r="N29" s="35"/>
       <c r="O29" s="36"/>
     </row>
-    <row r="30" spans="1:17" ht="34" customHeight="1">
+    <row r="30" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A30" s="35"/>
       <c r="B30" s="35"/>
       <c r="C30" s="35"/>
@@ -13265,7 +13181,7 @@
       <c r="N30" s="35"/>
       <c r="O30" s="36"/>
     </row>
-    <row r="31" spans="1:17" ht="34" customHeight="1">
+    <row r="31" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A31" s="35"/>
       <c r="B31" s="35"/>
       <c r="C31" s="35"/>
@@ -13282,7 +13198,7 @@
       <c r="N31" s="35"/>
       <c r="O31" s="36"/>
     </row>
-    <row r="32" spans="1:17" ht="34" customHeight="1">
+    <row r="32" spans="1:17" ht="33.950000000000003" customHeight="1">
       <c r="A32" s="35"/>
       <c r="B32" s="35"/>
       <c r="C32" s="35"/>
@@ -13299,7 +13215,7 @@
       <c r="N32" s="35"/>
       <c r="O32" s="36"/>
     </row>
-    <row r="33" spans="1:15" ht="34" customHeight="1">
+    <row r="33" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A33" s="35"/>
       <c r="B33" s="35"/>
       <c r="C33" s="35"/>
@@ -13316,7 +13232,7 @@
       <c r="N33" s="35"/>
       <c r="O33" s="36"/>
     </row>
-    <row r="34" spans="1:15" ht="34" customHeight="1">
+    <row r="34" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A34" s="35"/>
       <c r="B34" s="35"/>
       <c r="C34" s="35"/>
@@ -13333,7 +13249,7 @@
       <c r="N34" s="35"/>
       <c r="O34" s="36"/>
     </row>
-    <row r="35" spans="1:15" ht="34" customHeight="1">
+    <row r="35" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A35" s="35"/>
       <c r="B35" s="35"/>
       <c r="C35" s="35"/>
@@ -13350,7 +13266,7 @@
       <c r="N35" s="35"/>
       <c r="O35" s="36"/>
     </row>
-    <row r="36" spans="1:15" ht="34" customHeight="1">
+    <row r="36" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A36" s="35"/>
       <c r="B36" s="35"/>
       <c r="C36" s="35"/>
@@ -13367,7 +13283,7 @@
       <c r="N36" s="35"/>
       <c r="O36" s="36"/>
     </row>
-    <row r="37" spans="1:15" ht="34" customHeight="1">
+    <row r="37" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A37" s="35"/>
       <c r="B37" s="35"/>
       <c r="C37" s="35"/>
@@ -13384,7 +13300,7 @@
       <c r="N37" s="35"/>
       <c r="O37" s="36"/>
     </row>
-    <row r="38" spans="1:15" ht="34" customHeight="1">
+    <row r="38" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A38" s="35"/>
       <c r="B38" s="35"/>
       <c r="C38" s="35"/>
@@ -13401,7 +13317,7 @@
       <c r="N38" s="35"/>
       <c r="O38" s="36"/>
     </row>
-    <row r="39" spans="1:15" ht="34" customHeight="1">
+    <row r="39" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A39" s="35"/>
       <c r="B39" s="35"/>
       <c r="C39" s="35"/>
@@ -13418,7 +13334,7 @@
       <c r="N39" s="35"/>
       <c r="O39" s="36"/>
     </row>
-    <row r="40" spans="1:15" ht="34" customHeight="1">
+    <row r="40" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A40" s="35"/>
       <c r="B40" s="35"/>
       <c r="C40" s="35"/>
@@ -13435,7 +13351,7 @@
       <c r="N40" s="35"/>
       <c r="O40" s="36"/>
     </row>
-    <row r="41" spans="1:15" ht="34" customHeight="1">
+    <row r="41" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A41" s="35"/>
       <c r="B41" s="35"/>
       <c r="C41" s="35"/>
@@ -13452,7 +13368,7 @@
       <c r="N41" s="35"/>
       <c r="O41" s="36"/>
     </row>
-    <row r="42" spans="1:15" ht="34" customHeight="1">
+    <row r="42" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A42" s="35"/>
       <c r="B42" s="35"/>
       <c r="C42" s="35"/>
@@ -13469,7 +13385,7 @@
       <c r="N42" s="35"/>
       <c r="O42" s="36"/>
     </row>
-    <row r="43" spans="1:15" ht="34" customHeight="1">
+    <row r="43" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A43" s="35"/>
       <c r="B43" s="35"/>
       <c r="C43" s="35"/>
@@ -13486,7 +13402,7 @@
       <c r="N43" s="35"/>
       <c r="O43" s="36"/>
     </row>
-    <row r="44" spans="1:15" ht="34" customHeight="1">
+    <row r="44" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A44" s="35"/>
       <c r="B44" s="35"/>
       <c r="C44" s="35"/>
@@ -13503,7 +13419,7 @@
       <c r="N44" s="35"/>
       <c r="O44" s="36"/>
     </row>
-    <row r="45" spans="1:15" ht="34" customHeight="1">
+    <row r="45" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A45" s="35"/>
       <c r="B45" s="35"/>
       <c r="C45" s="35"/>
@@ -13520,7 +13436,7 @@
       <c r="N45" s="35"/>
       <c r="O45" s="36"/>
     </row>
-    <row r="46" spans="1:15" ht="34" customHeight="1">
+    <row r="46" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A46" s="35"/>
       <c r="B46" s="35"/>
       <c r="C46" s="35"/>
@@ -13537,7 +13453,7 @@
       <c r="N46" s="35"/>
       <c r="O46" s="36"/>
     </row>
-    <row r="47" spans="1:15" ht="34" customHeight="1">
+    <row r="47" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A47" s="35"/>
       <c r="B47" s="35"/>
       <c r="C47" s="35"/>
@@ -13554,7 +13470,7 @@
       <c r="N47" s="35"/>
       <c r="O47" s="36"/>
     </row>
-    <row r="48" spans="1:15" ht="34" customHeight="1">
+    <row r="48" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A48" s="35"/>
       <c r="B48" s="35"/>
       <c r="C48" s="35"/>
@@ -13571,7 +13487,7 @@
       <c r="N48" s="35"/>
       <c r="O48" s="36"/>
     </row>
-    <row r="49" spans="1:15" ht="34" customHeight="1">
+    <row r="49" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A49" s="35"/>
       <c r="B49" s="35"/>
       <c r="C49" s="35"/>
@@ -13588,7 +13504,7 @@
       <c r="N49" s="35"/>
       <c r="O49" s="36"/>
     </row>
-    <row r="50" spans="1:15" ht="34" customHeight="1">
+    <row r="50" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A50" s="35"/>
       <c r="B50" s="35"/>
       <c r="C50" s="35"/>
@@ -13605,7 +13521,7 @@
       <c r="N50" s="35"/>
       <c r="O50" s="36"/>
     </row>
-    <row r="51" spans="1:15" ht="34" customHeight="1">
+    <row r="51" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A51" s="35"/>
       <c r="B51" s="35"/>
       <c r="C51" s="35"/>
@@ -13622,7 +13538,7 @@
       <c r="N51" s="35"/>
       <c r="O51" s="36"/>
     </row>
-    <row r="52" spans="1:15" ht="34" customHeight="1">
+    <row r="52" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A52" s="35"/>
       <c r="B52" s="35"/>
       <c r="C52" s="35"/>
@@ -13639,7 +13555,7 @@
       <c r="N52" s="35"/>
       <c r="O52" s="36"/>
     </row>
-    <row r="53" spans="1:15" ht="34" customHeight="1">
+    <row r="53" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A53" s="35"/>
       <c r="B53" s="35"/>
       <c r="C53" s="35"/>
@@ -13656,7 +13572,7 @@
       <c r="N53" s="35"/>
       <c r="O53" s="36"/>
     </row>
-    <row r="54" spans="1:15" ht="34" customHeight="1">
+    <row r="54" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A54" s="35"/>
       <c r="B54" s="35"/>
       <c r="C54" s="35"/>
@@ -13673,7 +13589,7 @@
       <c r="N54" s="35"/>
       <c r="O54" s="36"/>
     </row>
-    <row r="55" spans="1:15" ht="34" customHeight="1">
+    <row r="55" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A55" s="35"/>
       <c r="B55" s="35"/>
       <c r="C55" s="35"/>
@@ -13690,7 +13606,7 @@
       <c r="N55" s="35"/>
       <c r="O55" s="36"/>
     </row>
-    <row r="56" spans="1:15" ht="34" customHeight="1">
+    <row r="56" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A56" s="35"/>
       <c r="B56" s="35"/>
       <c r="C56" s="35"/>
@@ -13707,7 +13623,7 @@
       <c r="N56" s="35"/>
       <c r="O56" s="36"/>
     </row>
-    <row r="57" spans="1:15" ht="34" customHeight="1">
+    <row r="57" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A57" s="35"/>
       <c r="B57" s="35"/>
       <c r="C57" s="35"/>
@@ -13724,7 +13640,7 @@
       <c r="N57" s="35"/>
       <c r="O57" s="36"/>
     </row>
-    <row r="58" spans="1:15" ht="34" customHeight="1">
+    <row r="58" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A58" s="35"/>
       <c r="B58" s="35"/>
       <c r="C58" s="35"/>
@@ -13741,7 +13657,7 @@
       <c r="N58" s="35"/>
       <c r="O58" s="36"/>
     </row>
-    <row r="59" spans="1:15" ht="34" customHeight="1">
+    <row r="59" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A59" s="35"/>
       <c r="B59" s="35"/>
       <c r="C59" s="35"/>
@@ -13758,7 +13674,7 @@
       <c r="N59" s="35"/>
       <c r="O59" s="36"/>
     </row>
-    <row r="60" spans="1:15" ht="34" customHeight="1">
+    <row r="60" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A60" s="35"/>
       <c r="B60" s="35"/>
       <c r="C60" s="35"/>
@@ -13775,7 +13691,7 @@
       <c r="N60" s="35"/>
       <c r="O60" s="28"/>
     </row>
-    <row r="61" spans="1:15" ht="34" customHeight="1">
+    <row r="61" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A61" s="35"/>
       <c r="B61" s="35"/>
       <c r="C61" s="35"/>
@@ -13792,7 +13708,7 @@
       <c r="N61" s="35"/>
       <c r="O61" s="36"/>
     </row>
-    <row r="62" spans="1:15" ht="34" customHeight="1">
+    <row r="62" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A62" s="35"/>
       <c r="B62" s="35"/>
       <c r="C62" s="35"/>
@@ -13809,7 +13725,7 @@
       <c r="N62" s="35"/>
       <c r="O62" s="36"/>
     </row>
-    <row r="63" spans="1:15" ht="34" customHeight="1">
+    <row r="63" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A63" s="35"/>
       <c r="B63" s="35"/>
       <c r="C63" s="35"/>
@@ -13826,7 +13742,7 @@
       <c r="N63" s="35"/>
       <c r="O63" s="36"/>
     </row>
-    <row r="64" spans="1:15" ht="34" customHeight="1">
+    <row r="64" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A64" s="35"/>
       <c r="B64" s="35"/>
       <c r="C64" s="35"/>
@@ -13843,7 +13759,7 @@
       <c r="N64" s="35"/>
       <c r="O64" s="36"/>
     </row>
-    <row r="65" spans="1:15" ht="34" customHeight="1">
+    <row r="65" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A65" s="35"/>
       <c r="B65" s="35"/>
       <c r="C65" s="35"/>
@@ -13860,7 +13776,7 @@
       <c r="N65" s="35"/>
       <c r="O65" s="28"/>
     </row>
-    <row r="66" spans="1:15" ht="34" customHeight="1">
+    <row r="66" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A66" s="35"/>
       <c r="B66" s="35"/>
       <c r="C66" s="35"/>
@@ -13877,7 +13793,7 @@
       <c r="N66" s="35"/>
       <c r="O66" s="28"/>
     </row>
-    <row r="67" spans="1:15" ht="34" customHeight="1">
+    <row r="67" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A67" s="35"/>
       <c r="B67" s="35"/>
       <c r="C67" s="35"/>
@@ -13894,7 +13810,7 @@
       <c r="N67" s="35"/>
       <c r="O67" s="36"/>
     </row>
-    <row r="68" spans="1:15" ht="34" customHeight="1">
+    <row r="68" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A68" s="35"/>
       <c r="B68" s="35"/>
       <c r="C68" s="35"/>
@@ -13911,7 +13827,7 @@
       <c r="N68" s="35"/>
       <c r="O68" s="36"/>
     </row>
-    <row r="69" spans="1:15" ht="34" customHeight="1">
+    <row r="69" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A69" s="35"/>
       <c r="B69" s="35"/>
       <c r="C69" s="35"/>
@@ -13928,7 +13844,7 @@
       <c r="N69" s="35"/>
       <c r="O69" s="36"/>
     </row>
-    <row r="70" spans="1:15" ht="34" customHeight="1">
+    <row r="70" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A70" s="35"/>
       <c r="B70" s="35"/>
       <c r="C70" s="35"/>
@@ -13945,7 +13861,7 @@
       <c r="N70" s="35"/>
       <c r="O70" s="36"/>
     </row>
-    <row r="71" spans="1:15" ht="34" customHeight="1">
+    <row r="71" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A71" s="35"/>
       <c r="B71" s="35"/>
       <c r="C71" s="35"/>
@@ -13962,7 +13878,7 @@
       <c r="N71" s="35"/>
       <c r="O71" s="36"/>
     </row>
-    <row r="72" spans="1:15" ht="34" customHeight="1">
+    <row r="72" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A72" s="35"/>
       <c r="B72" s="35"/>
       <c r="C72" s="35"/>
@@ -13979,7 +13895,7 @@
       <c r="N72" s="35"/>
       <c r="O72" s="36"/>
     </row>
-    <row r="73" spans="1:15" ht="34" customHeight="1">
+    <row r="73" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A73" s="35"/>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
@@ -13996,7 +13912,7 @@
       <c r="N73" s="35"/>
       <c r="O73" s="28"/>
     </row>
-    <row r="74" spans="1:15" ht="34" customHeight="1">
+    <row r="74" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A74" s="35"/>
       <c r="B74" s="35"/>
       <c r="C74" s="35"/>
@@ -14013,7 +13929,7 @@
       <c r="N74" s="35"/>
       <c r="O74" s="28"/>
     </row>
-    <row r="75" spans="1:15" ht="34" customHeight="1">
+    <row r="75" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A75" s="35"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -14030,7 +13946,7 @@
       <c r="N75" s="35"/>
       <c r="O75" s="36"/>
     </row>
-    <row r="76" spans="1:15" ht="34" customHeight="1">
+    <row r="76" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A76" s="35"/>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
@@ -14047,7 +13963,7 @@
       <c r="N76" s="35"/>
       <c r="O76" s="36"/>
     </row>
-    <row r="77" spans="1:15" ht="34" customHeight="1">
+    <row r="77" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A77" s="35"/>
       <c r="B77" s="35"/>
       <c r="C77" s="35"/>
@@ -14064,7 +13980,7 @@
       <c r="N77" s="35"/>
       <c r="O77" s="28"/>
     </row>
-    <row r="78" spans="1:15" ht="34" customHeight="1">
+    <row r="78" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A78" s="35"/>
       <c r="B78" s="35"/>
       <c r="C78" s="35"/>
@@ -14081,7 +13997,7 @@
       <c r="N78" s="35"/>
       <c r="O78" s="28"/>
     </row>
-    <row r="79" spans="1:15" ht="34" customHeight="1">
+    <row r="79" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A79" s="35"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -14098,7 +14014,7 @@
       <c r="N79" s="35"/>
       <c r="O79" s="36"/>
     </row>
-    <row r="80" spans="1:15" ht="34" customHeight="1">
+    <row r="80" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A80" s="35"/>
       <c r="B80" s="35"/>
       <c r="C80" s="35"/>
@@ -14115,7 +14031,7 @@
       <c r="N80" s="35"/>
       <c r="O80" s="28"/>
     </row>
-    <row r="81" spans="1:15" ht="34" customHeight="1">
+    <row r="81" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A81" s="35"/>
       <c r="B81" s="35"/>
       <c r="C81" s="35"/>
@@ -14132,7 +14048,7 @@
       <c r="N81" s="35"/>
       <c r="O81" s="28"/>
     </row>
-    <row r="82" spans="1:15" ht="34" customHeight="1">
+    <row r="82" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A82" s="35"/>
       <c r="B82" s="35"/>
       <c r="C82" s="35"/>
@@ -14149,7 +14065,7 @@
       <c r="N82" s="35"/>
       <c r="O82" s="28"/>
     </row>
-    <row r="83" spans="1:15" ht="34" customHeight="1">
+    <row r="83" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A83" s="35"/>
       <c r="B83" s="35"/>
       <c r="C83" s="35"/>
@@ -14166,7 +14082,7 @@
       <c r="N83" s="35"/>
       <c r="O83" s="28"/>
     </row>
-    <row r="84" spans="1:15" ht="34" customHeight="1">
+    <row r="84" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A84" s="35"/>
       <c r="B84" s="35"/>
       <c r="C84" s="35"/>
@@ -14183,7 +14099,7 @@
       <c r="N84" s="35"/>
       <c r="O84" s="28"/>
     </row>
-    <row r="85" spans="1:15" ht="34" customHeight="1">
+    <row r="85" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A85" s="35"/>
       <c r="B85" s="35"/>
       <c r="C85" s="35"/>
@@ -14200,7 +14116,7 @@
       <c r="N85" s="35"/>
       <c r="O85" s="28"/>
     </row>
-    <row r="86" spans="1:15" ht="34" customHeight="1">
+    <row r="86" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A86" s="35"/>
       <c r="B86" s="35"/>
       <c r="C86" s="35"/>
@@ -14217,7 +14133,7 @@
       <c r="N86" s="35"/>
       <c r="O86" s="28"/>
     </row>
-    <row r="87" spans="1:15" ht="34" customHeight="1">
+    <row r="87" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A87" s="35"/>
       <c r="B87" s="35"/>
       <c r="C87" s="35"/>
@@ -14234,7 +14150,7 @@
       <c r="N87" s="35"/>
       <c r="O87" s="28"/>
     </row>
-    <row r="88" spans="1:15" ht="34" customHeight="1">
+    <row r="88" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A88" s="35"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35"/>
@@ -14251,7 +14167,7 @@
       <c r="N88" s="35"/>
       <c r="O88" s="28"/>
     </row>
-    <row r="89" spans="1:15" ht="34" customHeight="1">
+    <row r="89" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A89" s="35"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35"/>
@@ -14268,7 +14184,7 @@
       <c r="N89" s="35"/>
       <c r="O89" s="28"/>
     </row>
-    <row r="90" spans="1:15" ht="34" customHeight="1">
+    <row r="90" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A90" s="35"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35"/>
@@ -14285,7 +14201,7 @@
       <c r="N90" s="35"/>
       <c r="O90" s="28"/>
     </row>
-    <row r="91" spans="1:15" ht="34" customHeight="1">
+    <row r="91" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A91" s="35"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35"/>
@@ -14302,7 +14218,7 @@
       <c r="N91" s="35"/>
       <c r="O91" s="28"/>
     </row>
-    <row r="92" spans="1:15" ht="34" customHeight="1">
+    <row r="92" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A92" s="35"/>
       <c r="B92" s="35"/>
       <c r="C92" s="35"/>
@@ -14319,7 +14235,7 @@
       <c r="N92" s="35"/>
       <c r="O92" s="28"/>
     </row>
-    <row r="93" spans="1:15" ht="34" customHeight="1">
+    <row r="93" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A93" s="35"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35"/>
@@ -14336,7 +14252,7 @@
       <c r="N93" s="35"/>
       <c r="O93" s="28"/>
     </row>
-    <row r="94" spans="1:15" ht="34" customHeight="1">
+    <row r="94" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A94" s="35"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35"/>
@@ -14353,7 +14269,7 @@
       <c r="N94" s="35"/>
       <c r="O94" s="28"/>
     </row>
-    <row r="95" spans="1:15" ht="34" customHeight="1">
+    <row r="95" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A95" s="35"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35"/>
@@ -14370,7 +14286,7 @@
       <c r="N95" s="35"/>
       <c r="O95" s="28"/>
     </row>
-    <row r="96" spans="1:15" ht="34" customHeight="1">
+    <row r="96" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A96" s="35"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35"/>
@@ -14387,7 +14303,7 @@
       <c r="N96" s="35"/>
       <c r="O96" s="28"/>
     </row>
-    <row r="97" spans="1:15" ht="34" customHeight="1">
+    <row r="97" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A97" s="35"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35"/>
@@ -14404,7 +14320,7 @@
       <c r="N97" s="35"/>
       <c r="O97" s="28"/>
     </row>
-    <row r="98" spans="1:15" ht="34" customHeight="1">
+    <row r="98" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A98" s="35"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35"/>
@@ -14421,7 +14337,7 @@
       <c r="N98" s="35"/>
       <c r="O98" s="28"/>
     </row>
-    <row r="99" spans="1:15" ht="34" customHeight="1">
+    <row r="99" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A99" s="35"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35"/>
@@ -14438,7 +14354,7 @@
       <c r="N99" s="35"/>
       <c r="O99" s="28"/>
     </row>
-    <row r="100" spans="1:15" ht="34" customHeight="1">
+    <row r="100" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A100" s="35"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35"/>
@@ -14455,7 +14371,7 @@
       <c r="N100" s="35"/>
       <c r="O100" s="28"/>
     </row>
-    <row r="101" spans="1:15" ht="34" customHeight="1">
+    <row r="101" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A101" s="35"/>
       <c r="B101" s="35"/>
       <c r="C101" s="35"/>
@@ -14472,7 +14388,7 @@
       <c r="N101" s="35"/>
       <c r="O101" s="28"/>
     </row>
-    <row r="102" spans="1:15" ht="34" customHeight="1">
+    <row r="102" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A102" s="35"/>
       <c r="B102" s="35"/>
       <c r="C102" s="35"/>
@@ -14489,7 +14405,7 @@
       <c r="N102" s="35"/>
       <c r="O102" s="28"/>
     </row>
-    <row r="103" spans="1:15" ht="34" customHeight="1">
+    <row r="103" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A103" s="35"/>
       <c r="B103" s="35"/>
       <c r="C103" s="35"/>
@@ -14506,7 +14422,7 @@
       <c r="N103" s="35"/>
       <c r="O103" s="28"/>
     </row>
-    <row r="104" spans="1:15" ht="34" customHeight="1">
+    <row r="104" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A104" s="35"/>
       <c r="B104" s="35"/>
       <c r="C104" s="35"/>
@@ -14523,7 +14439,7 @@
       <c r="N104" s="35"/>
       <c r="O104" s="28"/>
     </row>
-    <row r="105" spans="1:15" ht="34" customHeight="1">
+    <row r="105" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A105" s="35"/>
       <c r="B105" s="35"/>
       <c r="C105" s="35"/>
@@ -14540,7 +14456,7 @@
       <c r="N105" s="35"/>
       <c r="O105" s="28"/>
     </row>
-    <row r="106" spans="1:15" ht="34" customHeight="1">
+    <row r="106" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A106" s="35"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35"/>
@@ -14557,7 +14473,7 @@
       <c r="N106" s="35"/>
       <c r="O106" s="28"/>
     </row>
-    <row r="107" spans="1:15" ht="34" customHeight="1">
+    <row r="107" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A107" s="35"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35"/>
@@ -14574,7 +14490,7 @@
       <c r="N107" s="35"/>
       <c r="O107" s="28"/>
     </row>
-    <row r="108" spans="1:15" ht="34" customHeight="1">
+    <row r="108" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A108" s="35"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35"/>
@@ -14591,7 +14507,7 @@
       <c r="N108" s="35"/>
       <c r="O108" s="28"/>
     </row>
-    <row r="109" spans="1:15" ht="34" customHeight="1">
+    <row r="109" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A109" s="35"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35"/>
@@ -14608,7 +14524,7 @@
       <c r="N109" s="35"/>
       <c r="O109" s="28"/>
     </row>
-    <row r="110" spans="1:15" ht="34" customHeight="1">
+    <row r="110" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A110" s="35"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35"/>
@@ -14625,7 +14541,7 @@
       <c r="N110" s="35"/>
       <c r="O110" s="28"/>
     </row>
-    <row r="111" spans="1:15" ht="34" customHeight="1">
+    <row r="111" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A111" s="35"/>
       <c r="B111" s="35"/>
       <c r="C111" s="35"/>
@@ -14642,7 +14558,7 @@
       <c r="N111" s="35"/>
       <c r="O111" s="28"/>
     </row>
-    <row r="112" spans="1:15" ht="34" customHeight="1">
+    <row r="112" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A112" s="35"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35"/>
@@ -14659,7 +14575,7 @@
       <c r="N112" s="35"/>
       <c r="O112" s="28"/>
     </row>
-    <row r="113" spans="1:15" ht="34" customHeight="1">
+    <row r="113" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A113" s="35"/>
       <c r="B113" s="35"/>
       <c r="C113" s="35"/>
@@ -14676,7 +14592,7 @@
       <c r="N113" s="35"/>
       <c r="O113" s="28"/>
     </row>
-    <row r="114" spans="1:15" ht="34" customHeight="1">
+    <row r="114" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A114" s="35"/>
       <c r="B114" s="35"/>
       <c r="C114" s="35"/>
@@ -14693,7 +14609,7 @@
       <c r="N114" s="35"/>
       <c r="O114" s="28"/>
     </row>
-    <row r="115" spans="1:15" ht="34" customHeight="1">
+    <row r="115" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A115" s="35"/>
       <c r="B115" s="35"/>
       <c r="C115" s="35"/>
@@ -14710,7 +14626,7 @@
       <c r="N115" s="35"/>
       <c r="O115" s="28"/>
     </row>
-    <row r="116" spans="1:15" ht="34" customHeight="1">
+    <row r="116" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A116" s="35"/>
       <c r="B116" s="35"/>
       <c r="C116" s="35"/>
@@ -14727,7 +14643,7 @@
       <c r="N116" s="35"/>
       <c r="O116" s="28"/>
     </row>
-    <row r="117" spans="1:15" ht="34" customHeight="1">
+    <row r="117" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A117" s="35"/>
       <c r="B117" s="35"/>
       <c r="C117" s="35"/>
@@ -14744,7 +14660,7 @@
       <c r="N117" s="35"/>
       <c r="O117" s="28"/>
     </row>
-    <row r="118" spans="1:15" ht="34" customHeight="1">
+    <row r="118" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A118" s="35"/>
       <c r="B118" s="35"/>
       <c r="C118" s="35"/>
@@ -14761,7 +14677,7 @@
       <c r="N118" s="35"/>
       <c r="O118" s="28"/>
     </row>
-    <row r="119" spans="1:15" ht="34" customHeight="1">
+    <row r="119" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A119" s="35"/>
       <c r="B119" s="35"/>
       <c r="C119" s="35"/>
@@ -14778,7 +14694,7 @@
       <c r="N119" s="35"/>
       <c r="O119" s="28"/>
     </row>
-    <row r="120" spans="1:15" ht="34" customHeight="1">
+    <row r="120" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A120" s="35"/>
       <c r="B120" s="35"/>
       <c r="C120" s="35"/>
@@ -14795,7 +14711,7 @@
       <c r="N120" s="35"/>
       <c r="O120" s="28"/>
     </row>
-    <row r="121" spans="1:15" ht="34" customHeight="1">
+    <row r="121" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A121" s="35"/>
       <c r="B121" s="35"/>
       <c r="C121" s="35"/>
@@ -14812,7 +14728,7 @@
       <c r="N121" s="35"/>
       <c r="O121" s="28"/>
     </row>
-    <row r="122" spans="1:15" ht="34" customHeight="1">
+    <row r="122" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A122" s="35"/>
       <c r="B122" s="35"/>
       <c r="C122" s="35"/>
@@ -14829,7 +14745,7 @@
       <c r="N122" s="35"/>
       <c r="O122" s="28"/>
     </row>
-    <row r="123" spans="1:15" ht="34" customHeight="1">
+    <row r="123" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A123" s="35"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35"/>
@@ -14846,7 +14762,7 @@
       <c r="N123" s="35"/>
       <c r="O123" s="28"/>
     </row>
-    <row r="124" spans="1:15" ht="34" customHeight="1">
+    <row r="124" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A124" s="35"/>
       <c r="B124" s="35"/>
       <c r="C124" s="35"/>
@@ -14863,7 +14779,7 @@
       <c r="N124" s="35"/>
       <c r="O124" s="28"/>
     </row>
-    <row r="125" spans="1:15" ht="34" customHeight="1">
+    <row r="125" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A125" s="35"/>
       <c r="B125" s="35"/>
       <c r="C125" s="35"/>
@@ -14880,7 +14796,7 @@
       <c r="N125" s="35"/>
       <c r="O125" s="28"/>
     </row>
-    <row r="126" spans="1:15" ht="34" customHeight="1">
+    <row r="126" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A126" s="35"/>
       <c r="B126" s="35"/>
       <c r="C126" s="35"/>
@@ -14897,7 +14813,7 @@
       <c r="N126" s="35"/>
       <c r="O126" s="28"/>
     </row>
-    <row r="127" spans="1:15" ht="34" customHeight="1">
+    <row r="127" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A127" s="35"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35"/>
@@ -14914,7 +14830,7 @@
       <c r="N127" s="35"/>
       <c r="O127" s="28"/>
     </row>
-    <row r="128" spans="1:15" ht="34" customHeight="1">
+    <row r="128" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A128" s="35"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35"/>
@@ -14931,7 +14847,7 @@
       <c r="N128" s="35"/>
       <c r="O128" s="28"/>
     </row>
-    <row r="129" spans="1:15" ht="34" customHeight="1">
+    <row r="129" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A129" s="35"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35"/>
@@ -14948,7 +14864,7 @@
       <c r="N129" s="35"/>
       <c r="O129" s="28"/>
     </row>
-    <row r="130" spans="1:15" ht="34" customHeight="1">
+    <row r="130" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A130" s="35"/>
       <c r="B130" s="35"/>
       <c r="C130" s="35"/>
@@ -14965,7 +14881,7 @@
       <c r="N130" s="35"/>
       <c r="O130" s="28"/>
     </row>
-    <row r="131" spans="1:15" ht="34" customHeight="1">
+    <row r="131" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A131" s="35"/>
       <c r="B131" s="35"/>
       <c r="C131" s="35"/>
@@ -14982,7 +14898,7 @@
       <c r="N131" s="35"/>
       <c r="O131" s="28"/>
     </row>
-    <row r="132" spans="1:15" ht="34" customHeight="1">
+    <row r="132" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A132" s="35"/>
       <c r="B132" s="35"/>
       <c r="C132" s="35"/>
@@ -14999,7 +14915,7 @@
       <c r="N132" s="35"/>
       <c r="O132" s="28"/>
     </row>
-    <row r="133" spans="1:15" ht="34" customHeight="1">
+    <row r="133" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A133" s="35"/>
       <c r="B133" s="35"/>
       <c r="C133" s="35"/>
@@ -15016,7 +14932,7 @@
       <c r="N133" s="35"/>
       <c r="O133" s="28"/>
     </row>
-    <row r="134" spans="1:15" ht="34" customHeight="1">
+    <row r="134" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A134" s="35"/>
       <c r="B134" s="35"/>
       <c r="C134" s="35"/>
@@ -15033,7 +14949,7 @@
       <c r="N134" s="35"/>
       <c r="O134" s="28"/>
     </row>
-    <row r="135" spans="1:15" ht="34" customHeight="1">
+    <row r="135" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A135" s="35"/>
       <c r="B135" s="35"/>
       <c r="C135" s="35"/>
@@ -15050,7 +14966,7 @@
       <c r="N135" s="35"/>
       <c r="O135" s="28"/>
     </row>
-    <row r="136" spans="1:15" ht="34" customHeight="1">
+    <row r="136" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A136" s="35"/>
       <c r="B136" s="35"/>
       <c r="C136" s="35"/>
@@ -15067,7 +14983,7 @@
       <c r="N136" s="35"/>
       <c r="O136" s="28"/>
     </row>
-    <row r="137" spans="1:15" ht="34" customHeight="1">
+    <row r="137" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A137" s="35"/>
       <c r="B137" s="35"/>
       <c r="C137" s="35"/>
@@ -15084,7 +15000,7 @@
       <c r="N137" s="35"/>
       <c r="O137" s="28"/>
     </row>
-    <row r="138" spans="1:15" ht="34" customHeight="1">
+    <row r="138" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A138" s="35"/>
       <c r="B138" s="35"/>
       <c r="C138" s="35"/>
@@ -15101,7 +15017,7 @@
       <c r="N138" s="35"/>
       <c r="O138" s="28"/>
     </row>
-    <row r="139" spans="1:15" ht="34" customHeight="1">
+    <row r="139" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A139" s="35"/>
       <c r="B139" s="35"/>
       <c r="C139" s="35"/>
@@ -15118,7 +15034,7 @@
       <c r="N139" s="35"/>
       <c r="O139" s="28"/>
     </row>
-    <row r="140" spans="1:15" ht="34" customHeight="1">
+    <row r="140" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A140" s="35"/>
       <c r="B140" s="35"/>
       <c r="C140" s="35"/>
@@ -15135,7 +15051,7 @@
       <c r="N140" s="35"/>
       <c r="O140" s="28"/>
     </row>
-    <row r="141" spans="1:15" ht="34" customHeight="1">
+    <row r="141" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A141" s="35"/>
       <c r="B141" s="35"/>
       <c r="C141" s="35"/>
@@ -15152,7 +15068,7 @@
       <c r="N141" s="35"/>
       <c r="O141" s="28"/>
     </row>
-    <row r="142" spans="1:15" ht="34" customHeight="1">
+    <row r="142" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A142" s="35"/>
       <c r="B142" s="35"/>
       <c r="C142" s="35"/>
@@ -15169,7 +15085,7 @@
       <c r="N142" s="35"/>
       <c r="O142" s="28"/>
     </row>
-    <row r="143" spans="1:15" ht="34" customHeight="1">
+    <row r="143" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A143" s="35"/>
       <c r="B143" s="35"/>
       <c r="C143" s="35"/>
@@ -15186,7 +15102,7 @@
       <c r="N143" s="35"/>
       <c r="O143" s="28"/>
     </row>
-    <row r="144" spans="1:15" ht="34" customHeight="1">
+    <row r="144" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A144" s="35"/>
       <c r="B144" s="35"/>
       <c r="C144" s="35"/>
@@ -15203,7 +15119,7 @@
       <c r="N144" s="35"/>
       <c r="O144" s="28"/>
     </row>
-    <row r="145" spans="1:15" ht="34" customHeight="1">
+    <row r="145" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A145" s="35"/>
       <c r="B145" s="35"/>
       <c r="C145" s="35"/>
@@ -15220,7 +15136,7 @@
       <c r="N145" s="35"/>
       <c r="O145" s="28"/>
     </row>
-    <row r="146" spans="1:15" ht="34" customHeight="1">
+    <row r="146" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A146" s="35"/>
       <c r="B146" s="35"/>
       <c r="C146" s="35"/>
@@ -15237,7 +15153,7 @@
       <c r="N146" s="35"/>
       <c r="O146" s="28"/>
     </row>
-    <row r="147" spans="1:15" ht="34" customHeight="1">
+    <row r="147" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A147" s="35"/>
       <c r="B147" s="35"/>
       <c r="C147" s="35"/>
@@ -15254,7 +15170,7 @@
       <c r="N147" s="35"/>
       <c r="O147" s="28"/>
     </row>
-    <row r="148" spans="1:15" ht="34" customHeight="1">
+    <row r="148" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A148" s="35"/>
       <c r="B148" s="35"/>
       <c r="C148" s="35"/>
@@ -15271,7 +15187,7 @@
       <c r="N148" s="35"/>
       <c r="O148" s="28"/>
     </row>
-    <row r="149" spans="1:15" ht="34" customHeight="1">
+    <row r="149" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A149" s="35"/>
       <c r="B149" s="35"/>
       <c r="C149" s="35"/>
@@ -15288,7 +15204,7 @@
       <c r="N149" s="35"/>
       <c r="O149" s="28"/>
     </row>
-    <row r="150" spans="1:15" ht="34" customHeight="1">
+    <row r="150" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A150" s="35"/>
       <c r="B150" s="35"/>
       <c r="C150" s="35"/>
@@ -15305,7 +15221,7 @@
       <c r="N150" s="35"/>
       <c r="O150" s="28"/>
     </row>
-    <row r="151" spans="1:15" ht="34" customHeight="1">
+    <row r="151" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A151" s="35"/>
       <c r="B151" s="35"/>
       <c r="C151" s="35"/>
@@ -15322,7 +15238,7 @@
       <c r="N151" s="35"/>
       <c r="O151" s="28"/>
     </row>
-    <row r="152" spans="1:15" ht="34" customHeight="1">
+    <row r="152" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A152" s="35"/>
       <c r="B152" s="35"/>
       <c r="C152" s="35"/>
@@ -15339,7 +15255,7 @@
       <c r="N152" s="35"/>
       <c r="O152" s="28"/>
     </row>
-    <row r="153" spans="1:15" ht="34" customHeight="1">
+    <row r="153" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A153" s="35"/>
       <c r="B153" s="35"/>
       <c r="C153" s="35"/>
@@ -15356,7 +15272,7 @@
       <c r="N153" s="35"/>
       <c r="O153" s="28"/>
     </row>
-    <row r="154" spans="1:15" ht="34" customHeight="1">
+    <row r="154" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A154" s="35"/>
       <c r="B154" s="35"/>
       <c r="C154" s="35"/>
@@ -15373,7 +15289,7 @@
       <c r="N154" s="35"/>
       <c r="O154" s="28"/>
     </row>
-    <row r="155" spans="1:15" ht="34" customHeight="1">
+    <row r="155" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A155" s="35"/>
       <c r="B155" s="35"/>
       <c r="C155" s="35"/>
@@ -15390,7 +15306,7 @@
       <c r="N155" s="35"/>
       <c r="O155" s="28"/>
     </row>
-    <row r="156" spans="1:15" ht="34" customHeight="1">
+    <row r="156" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A156" s="35"/>
       <c r="B156" s="35"/>
       <c r="C156" s="35"/>
@@ -15407,7 +15323,7 @@
       <c r="N156" s="35"/>
       <c r="O156" s="28"/>
     </row>
-    <row r="157" spans="1:15" ht="34" customHeight="1">
+    <row r="157" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A157" s="35"/>
       <c r="B157" s="35"/>
       <c r="C157" s="35"/>
@@ -15424,7 +15340,7 @@
       <c r="N157" s="35"/>
       <c r="O157" s="28"/>
     </row>
-    <row r="158" spans="1:15" ht="34" customHeight="1">
+    <row r="158" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A158" s="35"/>
       <c r="B158" s="35"/>
       <c r="C158" s="35"/>
@@ -15441,7 +15357,7 @@
       <c r="N158" s="35"/>
       <c r="O158" s="28"/>
     </row>
-    <row r="159" spans="1:15" ht="34" customHeight="1">
+    <row r="159" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A159" s="35"/>
       <c r="B159" s="35"/>
       <c r="C159" s="35"/>
@@ -15458,7 +15374,7 @@
       <c r="N159" s="35"/>
       <c r="O159" s="28"/>
     </row>
-    <row r="160" spans="1:15" ht="34" customHeight="1">
+    <row r="160" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A160" s="35"/>
       <c r="B160" s="35"/>
       <c r="C160" s="35"/>
@@ -15475,7 +15391,7 @@
       <c r="N160" s="35"/>
       <c r="O160" s="28"/>
     </row>
-    <row r="161" spans="1:15" ht="34" customHeight="1">
+    <row r="161" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A161" s="35"/>
       <c r="B161" s="35"/>
       <c r="C161" s="35"/>
@@ -15492,7 +15408,7 @@
       <c r="N161" s="35"/>
       <c r="O161" s="28"/>
     </row>
-    <row r="162" spans="1:15" ht="34" customHeight="1">
+    <row r="162" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A162" s="35"/>
       <c r="B162" s="35"/>
       <c r="C162" s="35"/>
@@ -15509,7 +15425,7 @@
       <c r="N162" s="35"/>
       <c r="O162" s="28"/>
     </row>
-    <row r="163" spans="1:15" ht="34" customHeight="1">
+    <row r="163" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A163" s="35"/>
       <c r="B163" s="35"/>
       <c r="C163" s="35"/>
@@ -15526,7 +15442,7 @@
       <c r="N163" s="35"/>
       <c r="O163" s="28"/>
     </row>
-    <row r="164" spans="1:15" ht="34" customHeight="1">
+    <row r="164" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A164" s="35"/>
       <c r="B164" s="35"/>
       <c r="C164" s="35"/>
@@ -15543,7 +15459,7 @@
       <c r="N164" s="35"/>
       <c r="O164" s="28"/>
     </row>
-    <row r="165" spans="1:15" ht="34" customHeight="1">
+    <row r="165" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A165" s="35"/>
       <c r="B165" s="35"/>
       <c r="C165" s="35"/>
@@ -15560,7 +15476,7 @@
       <c r="N165" s="35"/>
       <c r="O165" s="28"/>
     </row>
-    <row r="166" spans="1:15" ht="34" customHeight="1">
+    <row r="166" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A166" s="35"/>
       <c r="B166" s="35"/>
       <c r="C166" s="35"/>
@@ -15577,7 +15493,7 @@
       <c r="N166" s="35"/>
       <c r="O166" s="28"/>
     </row>
-    <row r="167" spans="1:15" ht="34" customHeight="1">
+    <row r="167" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A167" s="35"/>
       <c r="B167" s="35"/>
       <c r="C167" s="35"/>
@@ -15594,7 +15510,7 @@
       <c r="N167" s="35"/>
       <c r="O167" s="28"/>
     </row>
-    <row r="168" spans="1:15" ht="34" customHeight="1">
+    <row r="168" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A168" s="35"/>
       <c r="B168" s="35"/>
       <c r="C168" s="35"/>
@@ -15611,7 +15527,7 @@
       <c r="N168" s="35"/>
       <c r="O168" s="28"/>
     </row>
-    <row r="169" spans="1:15" ht="34" customHeight="1">
+    <row r="169" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A169" s="35"/>
       <c r="B169" s="35"/>
       <c r="C169" s="35"/>
@@ -15628,7 +15544,7 @@
       <c r="N169" s="35"/>
       <c r="O169" s="28"/>
     </row>
-    <row r="170" spans="1:15" ht="34" customHeight="1">
+    <row r="170" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A170" s="35"/>
       <c r="B170" s="35"/>
       <c r="C170" s="35"/>
@@ -15645,7 +15561,7 @@
       <c r="N170" s="35"/>
       <c r="O170" s="28"/>
     </row>
-    <row r="171" spans="1:15" ht="34" customHeight="1">
+    <row r="171" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A171" s="35"/>
       <c r="B171" s="35"/>
       <c r="C171" s="35"/>
@@ -15662,7 +15578,7 @@
       <c r="N171" s="35"/>
       <c r="O171" s="28"/>
     </row>
-    <row r="172" spans="1:15" ht="34" customHeight="1">
+    <row r="172" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A172" s="35"/>
       <c r="B172" s="35"/>
       <c r="C172" s="35"/>
@@ -15679,7 +15595,7 @@
       <c r="N172" s="35"/>
       <c r="O172" s="28"/>
     </row>
-    <row r="173" spans="1:15" ht="34" customHeight="1">
+    <row r="173" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A173" s="35"/>
       <c r="B173" s="35"/>
       <c r="C173" s="35"/>
@@ -15696,7 +15612,7 @@
       <c r="N173" s="35"/>
       <c r="O173" s="28"/>
     </row>
-    <row r="174" spans="1:15" ht="34" customHeight="1">
+    <row r="174" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A174" s="35"/>
       <c r="B174" s="35"/>
       <c r="C174" s="35"/>
@@ -15713,7 +15629,7 @@
       <c r="N174" s="35"/>
       <c r="O174" s="28"/>
     </row>
-    <row r="175" spans="1:15" ht="34" customHeight="1">
+    <row r="175" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A175" s="35"/>
       <c r="B175" s="35"/>
       <c r="C175" s="35"/>
@@ -15730,7 +15646,7 @@
       <c r="N175" s="35"/>
       <c r="O175" s="28"/>
     </row>
-    <row r="176" spans="1:15" ht="34" customHeight="1">
+    <row r="176" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A176" s="35"/>
       <c r="B176" s="35"/>
       <c r="C176" s="35"/>
@@ -15747,7 +15663,7 @@
       <c r="N176" s="35"/>
       <c r="O176" s="28"/>
     </row>
-    <row r="177" spans="1:15" ht="34" customHeight="1">
+    <row r="177" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A177" s="35"/>
       <c r="B177" s="35"/>
       <c r="C177" s="35"/>
@@ -15764,7 +15680,7 @@
       <c r="N177" s="35"/>
       <c r="O177" s="28"/>
     </row>
-    <row r="178" spans="1:15" ht="34" customHeight="1">
+    <row r="178" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A178" s="35"/>
       <c r="B178" s="35"/>
       <c r="C178" s="35"/>
@@ -15781,7 +15697,7 @@
       <c r="N178" s="35"/>
       <c r="O178" s="28"/>
     </row>
-    <row r="179" spans="1:15" ht="34" customHeight="1">
+    <row r="179" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A179" s="35"/>
       <c r="B179" s="35"/>
       <c r="C179" s="35"/>
@@ -15798,7 +15714,7 @@
       <c r="N179" s="35"/>
       <c r="O179" s="28"/>
     </row>
-    <row r="180" spans="1:15" ht="34" customHeight="1">
+    <row r="180" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A180" s="35"/>
       <c r="B180" s="35"/>
       <c r="C180" s="35"/>
@@ -15815,7 +15731,7 @@
       <c r="N180" s="35"/>
       <c r="O180" s="28"/>
     </row>
-    <row r="181" spans="1:15" ht="34" customHeight="1">
+    <row r="181" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A181" s="35"/>
       <c r="B181" s="35"/>
       <c r="C181" s="35"/>
@@ -15832,7 +15748,7 @@
       <c r="N181" s="35"/>
       <c r="O181" s="28"/>
     </row>
-    <row r="182" spans="1:15" ht="34" customHeight="1">
+    <row r="182" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A182" s="35"/>
       <c r="B182" s="35"/>
       <c r="C182" s="35"/>
@@ -15849,7 +15765,7 @@
       <c r="N182" s="35"/>
       <c r="O182" s="28"/>
     </row>
-    <row r="183" spans="1:15" ht="34" customHeight="1">
+    <row r="183" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A183" s="35"/>
       <c r="B183" s="35"/>
       <c r="C183" s="35"/>
@@ -15866,7 +15782,7 @@
       <c r="N183" s="35"/>
       <c r="O183" s="28"/>
     </row>
-    <row r="184" spans="1:15" ht="34" customHeight="1">
+    <row r="184" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A184" s="35"/>
       <c r="B184" s="35"/>
       <c r="C184" s="35"/>
@@ -15883,7 +15799,7 @@
       <c r="N184" s="35"/>
       <c r="O184" s="28"/>
     </row>
-    <row r="185" spans="1:15" ht="34" customHeight="1">
+    <row r="185" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A185" s="35"/>
       <c r="B185" s="35"/>
       <c r="C185" s="35"/>
@@ -15900,7 +15816,7 @@
       <c r="N185" s="35"/>
       <c r="O185" s="28"/>
     </row>
-    <row r="186" spans="1:15" ht="34" customHeight="1">
+    <row r="186" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A186" s="35"/>
       <c r="B186" s="35"/>
       <c r="C186" s="35"/>
@@ -15917,7 +15833,7 @@
       <c r="N186" s="35"/>
       <c r="O186" s="28"/>
     </row>
-    <row r="187" spans="1:15" ht="34" customHeight="1">
+    <row r="187" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A187" s="35"/>
       <c r="B187" s="35"/>
       <c r="C187" s="35"/>
@@ -15934,7 +15850,7 @@
       <c r="N187" s="35"/>
       <c r="O187" s="28"/>
     </row>
-    <row r="188" spans="1:15" ht="34" customHeight="1">
+    <row r="188" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A188" s="35"/>
       <c r="B188" s="35"/>
       <c r="C188" s="35"/>
@@ -15951,7 +15867,7 @@
       <c r="N188" s="35"/>
       <c r="O188" s="28"/>
     </row>
-    <row r="189" spans="1:15" ht="34" customHeight="1">
+    <row r="189" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A189" s="35"/>
       <c r="B189" s="35"/>
       <c r="C189" s="35"/>
@@ -15968,7 +15884,7 @@
       <c r="N189" s="35"/>
       <c r="O189" s="28"/>
     </row>
-    <row r="190" spans="1:15" ht="34" customHeight="1">
+    <row r="190" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A190" s="35"/>
       <c r="B190" s="35"/>
       <c r="C190" s="35"/>
@@ -15985,7 +15901,7 @@
       <c r="N190" s="35"/>
       <c r="O190" s="28"/>
     </row>
-    <row r="191" spans="1:15" ht="34" customHeight="1">
+    <row r="191" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A191" s="35"/>
       <c r="B191" s="35"/>
       <c r="C191" s="35"/>
@@ -16002,7 +15918,7 @@
       <c r="N191" s="35"/>
       <c r="O191" s="28"/>
     </row>
-    <row r="192" spans="1:15" ht="34" customHeight="1">
+    <row r="192" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A192" s="35"/>
       <c r="B192" s="35"/>
       <c r="C192" s="35"/>
@@ -16019,7 +15935,7 @@
       <c r="N192" s="35"/>
       <c r="O192" s="28"/>
     </row>
-    <row r="193" spans="1:15" ht="34" customHeight="1">
+    <row r="193" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A193" s="35"/>
       <c r="B193" s="35"/>
       <c r="C193" s="35"/>
@@ -16036,7 +15952,7 @@
       <c r="N193" s="35"/>
       <c r="O193" s="28"/>
     </row>
-    <row r="194" spans="1:15" ht="34" customHeight="1">
+    <row r="194" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A194" s="35"/>
       <c r="B194" s="35"/>
       <c r="C194" s="35"/>
@@ -16053,7 +15969,7 @@
       <c r="N194" s="35"/>
       <c r="O194" s="28"/>
     </row>
-    <row r="195" spans="1:15" ht="34" customHeight="1">
+    <row r="195" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A195" s="35"/>
       <c r="B195" s="35"/>
       <c r="C195" s="35"/>
@@ -16070,7 +15986,7 @@
       <c r="N195" s="35"/>
       <c r="O195" s="28"/>
     </row>
-    <row r="196" spans="1:15" ht="34" customHeight="1">
+    <row r="196" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A196" s="35"/>
       <c r="B196" s="35"/>
       <c r="C196" s="35"/>
@@ -16087,7 +16003,7 @@
       <c r="N196" s="35"/>
       <c r="O196" s="28"/>
     </row>
-    <row r="197" spans="1:15" ht="34" customHeight="1">
+    <row r="197" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A197" s="35"/>
       <c r="B197" s="35"/>
       <c r="C197" s="35"/>
@@ -16104,7 +16020,7 @@
       <c r="N197" s="35"/>
       <c r="O197" s="28"/>
     </row>
-    <row r="198" spans="1:15" ht="34" customHeight="1">
+    <row r="198" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A198" s="37"/>
       <c r="B198" s="13"/>
       <c r="C198" s="13"/>
@@ -16121,7 +16037,7 @@
       <c r="N198" s="37"/>
       <c r="O198" s="37"/>
     </row>
-    <row r="199" spans="1:15" ht="34" customHeight="1">
+    <row r="199" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A199" s="37"/>
       <c r="B199" s="13"/>
       <c r="C199" s="13"/>
@@ -16138,7 +16054,7 @@
       <c r="N199" s="37"/>
       <c r="O199" s="37"/>
     </row>
-    <row r="200" spans="1:15" ht="34" customHeight="1">
+    <row r="200" spans="1:15" ht="33.950000000000003" customHeight="1">
       <c r="A200" s="37"/>
       <c r="B200" s="13"/>
       <c r="C200" s="13"/>
@@ -16184,47 +16100,47 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P320"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="3" customWidth="1"/>
-    <col min="3" max="3" width="46.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="40.1640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="101.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="46.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="101.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="14" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22" customHeight="1">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1">
+      <c r="A1" s="95" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47"/>
-    </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1">
-      <c r="A2" s="49" t="s">
+      <c r="B1" s="92"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="92"/>
+    </row>
+    <row r="2" spans="1:6" ht="21.95" customHeight="1">
+      <c r="A2" s="94" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="47"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="92"/>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="91" t="s">
         <v>404</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="47"/>
-    </row>
-    <row r="4" spans="1:6" ht="40" customHeight="1">
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="92"/>
+    </row>
+    <row r="4" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>3</v>
       </c>
@@ -18325,7 +18241,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="40" customHeight="1">
+    <row r="109" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A109" s="16" t="s">
         <v>108</v>
       </c>
@@ -18345,7 +18261,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="40" customHeight="1">
+    <row r="110" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A110" s="16" t="s">
         <v>108</v>
       </c>
@@ -18365,7 +18281,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="40" customHeight="1">
+    <row r="111" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A111" s="16" t="s">
         <v>108</v>
       </c>
@@ -18385,7 +18301,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="40" customHeight="1">
+    <row r="112" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A112" s="16" t="s">
         <v>108</v>
       </c>
@@ -18405,7 +18321,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="40" customHeight="1">
+    <row r="113" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A113" s="16" t="s">
         <v>108</v>
       </c>
@@ -18425,7 +18341,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="40" customHeight="1">
+    <row r="114" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A114" s="16" t="s">
         <v>108</v>
       </c>
@@ -18445,7 +18361,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="40" customHeight="1">
+    <row r="115" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A115" s="16" t="s">
         <v>109</v>
       </c>
@@ -18465,7 +18381,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="40" customHeight="1">
+    <row r="116" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A116" s="16" t="s">
         <v>109</v>
       </c>
@@ -18485,7 +18401,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="40" customHeight="1">
+    <row r="117" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A117" s="16" t="s">
         <v>109</v>
       </c>
@@ -18505,7 +18421,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="40" customHeight="1">
+    <row r="118" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A118" s="16" t="s">
         <v>109</v>
       </c>
@@ -18525,7 +18441,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="40" customHeight="1">
+    <row r="119" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A119" s="16" t="s">
         <v>109</v>
       </c>
@@ -18545,7 +18461,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="40" customHeight="1">
+    <row r="120" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A120" s="16" t="s">
         <v>109</v>
       </c>
@@ -18565,7 +18481,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="40" customHeight="1">
+    <row r="121" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A121" s="16" t="s">
         <v>109</v>
       </c>
@@ -18585,7 +18501,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="40" customHeight="1">
+    <row r="122" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A122" s="16" t="s">
         <v>109</v>
       </c>
@@ -18605,7 +18521,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="40" customHeight="1">
+    <row r="123" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A123" s="16" t="s">
         <v>109</v>
       </c>
@@ -18625,7 +18541,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="40" customHeight="1">
+    <row r="124" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A124" s="16" t="s">
         <v>109</v>
       </c>
@@ -18645,7 +18561,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="40" customHeight="1">
+    <row r="125" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A125" s="16" t="s">
         <v>109</v>
       </c>
@@ -18665,7 +18581,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="40" customHeight="1">
+    <row r="126" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A126" s="16" t="s">
         <v>109</v>
       </c>
@@ -18685,7 +18601,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="40" customHeight="1">
+    <row r="127" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A127" s="16" t="s">
         <v>109</v>
       </c>
@@ -18705,7 +18621,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="40" customHeight="1">
+    <row r="128" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A128" s="16" t="s">
         <v>109</v>
       </c>
@@ -18725,7 +18641,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="40" customHeight="1">
+    <row r="129" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A129" s="16" t="s">
         <v>110</v>
       </c>
@@ -18745,7 +18661,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="40" customHeight="1">
+    <row r="130" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A130" s="16" t="s">
         <v>110</v>
       </c>
@@ -18765,7 +18681,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="40" customHeight="1">
+    <row r="131" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A131" s="16" t="s">
         <v>110</v>
       </c>
@@ -18785,7 +18701,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="40" customHeight="1">
+    <row r="132" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A132" s="16" t="s">
         <v>110</v>
       </c>
@@ -18805,7 +18721,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="40" customHeight="1">
+    <row r="133" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A133" s="16" t="s">
         <v>110</v>
       </c>
@@ -18825,7 +18741,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="40" customHeight="1">
+    <row r="134" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A134" s="16" t="s">
         <v>110</v>
       </c>
@@ -18845,7 +18761,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="40" customHeight="1">
+    <row r="135" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A135" s="16" t="s">
         <v>110</v>
       </c>
@@ -18865,7 +18781,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="40" customHeight="1">
+    <row r="136" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A136" s="16" t="s">
         <v>110</v>
       </c>
@@ -18885,7 +18801,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="40" customHeight="1">
+    <row r="137" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A137" s="16" t="s">
         <v>110</v>
       </c>
@@ -18905,7 +18821,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="40" customHeight="1">
+    <row r="138" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A138" s="16" t="s">
         <v>110</v>
       </c>
@@ -18925,7 +18841,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="40" customHeight="1">
+    <row r="139" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A139" s="16" t="s">
         <v>110</v>
       </c>
@@ -18945,7 +18861,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="40" customHeight="1">
+    <row r="140" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A140" s="16" t="s">
         <v>110</v>
       </c>
@@ -18965,7 +18881,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="40" customHeight="1">
+    <row r="141" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A141" s="16" t="s">
         <v>110</v>
       </c>
@@ -18985,7 +18901,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="40" customHeight="1">
+    <row r="142" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A142" s="16" t="s">
         <v>111</v>
       </c>
@@ -19005,7 +18921,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="40" customHeight="1">
+    <row r="143" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A143" s="16" t="s">
         <v>111</v>
       </c>
@@ -19025,7 +18941,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="40" customHeight="1">
+    <row r="144" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A144" s="16" t="s">
         <v>111</v>
       </c>
@@ -19045,7 +18961,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="40" customHeight="1">
+    <row r="145" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A145" s="16" t="s">
         <v>111</v>
       </c>
@@ -19065,7 +18981,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="40" customHeight="1">
+    <row r="146" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A146" s="16" t="s">
         <v>111</v>
       </c>
@@ -19085,7 +19001,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="40" customHeight="1">
+    <row r="147" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A147" s="16" t="s">
         <v>111</v>
       </c>
@@ -19105,7 +19021,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="40" customHeight="1">
+    <row r="148" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A148" s="16" t="s">
         <v>111</v>
       </c>
@@ -19125,7 +19041,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="40" customHeight="1">
+    <row r="149" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A149" s="16" t="s">
         <v>111</v>
       </c>
@@ -19145,7 +19061,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="40" customHeight="1">
+    <row r="150" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A150" s="16" t="s">
         <v>111</v>
       </c>
@@ -19165,7 +19081,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="40" customHeight="1">
+    <row r="151" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A151" s="16" t="s">
         <v>111</v>
       </c>
@@ -19185,7 +19101,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="40" customHeight="1">
+    <row r="152" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A152" s="16" t="s">
         <v>111</v>
       </c>
@@ -19205,7 +19121,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="40" customHeight="1">
+    <row r="153" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A153" s="16" t="s">
         <v>111</v>
       </c>
@@ -19225,7 +19141,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="40" customHeight="1">
+    <row r="154" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A154" s="16" t="s">
         <v>111</v>
       </c>
@@ -19245,7 +19161,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="40" customHeight="1">
+    <row r="155" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A155" s="16" t="s">
         <v>112</v>
       </c>
@@ -19265,7 +19181,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="40" customHeight="1">
+    <row r="156" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A156" s="16" t="s">
         <v>112</v>
       </c>
@@ -19285,7 +19201,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="40" customHeight="1">
+    <row r="157" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A157" s="16" t="s">
         <v>112</v>
       </c>
@@ -19305,7 +19221,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="40" customHeight="1">
+    <row r="158" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A158" s="16" t="s">
         <v>112</v>
       </c>
@@ -19325,7 +19241,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="40" customHeight="1">
+    <row r="159" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A159" s="16" t="s">
         <v>112</v>
       </c>
@@ -19345,7 +19261,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="40" customHeight="1">
+    <row r="160" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A160" s="16" t="s">
         <v>112</v>
       </c>
@@ -19365,7 +19281,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="40" customHeight="1">
+    <row r="161" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A161" s="16" t="s">
         <v>112</v>
       </c>
@@ -19385,7 +19301,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="40" customHeight="1">
+    <row r="162" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A162" s="16" t="s">
         <v>112</v>
       </c>
@@ -19405,7 +19321,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="40" customHeight="1">
+    <row r="163" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A163" s="16" t="s">
         <v>112</v>
       </c>
@@ -19425,7 +19341,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="40" customHeight="1">
+    <row r="164" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A164" s="16" t="s">
         <v>112</v>
       </c>
@@ -19445,7 +19361,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="40" customHeight="1">
+    <row r="165" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A165" s="16" t="s">
         <v>112</v>
       </c>
@@ -19465,7 +19381,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="40" customHeight="1">
+    <row r="166" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A166" s="16" t="s">
         <v>112</v>
       </c>
@@ -19485,7 +19401,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="40" customHeight="1">
+    <row r="167" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A167" s="16" t="s">
         <v>112</v>
       </c>
@@ -19505,7 +19421,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="40" customHeight="1">
+    <row r="168" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A168" s="16" t="s">
         <v>112</v>
       </c>
@@ -19525,7 +19441,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="40" customHeight="1">
+    <row r="169" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A169" s="16" t="s">
         <v>112</v>
       </c>
@@ -19545,7 +19461,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="40" customHeight="1">
+    <row r="170" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A170" s="16" t="s">
         <v>112</v>
       </c>
@@ -19565,7 +19481,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="40" customHeight="1">
+    <row r="171" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A171" s="16" t="s">
         <v>112</v>
       </c>
@@ -19585,7 +19501,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="40" customHeight="1">
+    <row r="172" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A172" s="16" t="s">
         <v>112</v>
       </c>
@@ -19605,7 +19521,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="40" customHeight="1">
+    <row r="173" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A173" s="16" t="s">
         <v>114</v>
       </c>
@@ -19625,7 +19541,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="40" customHeight="1">
+    <row r="174" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A174" s="16" t="s">
         <v>114</v>
       </c>
@@ -19645,7 +19561,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="40" customHeight="1">
+    <row r="175" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A175" s="16" t="s">
         <v>114</v>
       </c>
@@ -19665,7 +19581,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="40" customHeight="1">
+    <row r="176" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A176" s="16" t="s">
         <v>114</v>
       </c>
@@ -19685,7 +19601,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="40" customHeight="1">
+    <row r="177" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A177" s="16" t="s">
         <v>114</v>
       </c>
@@ -19705,7 +19621,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="40" customHeight="1">
+    <row r="178" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A178" s="16" t="s">
         <v>114</v>
       </c>
@@ -19725,7 +19641,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="40" customHeight="1">
+    <row r="179" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A179" s="16" t="s">
         <v>114</v>
       </c>
@@ -19745,7 +19661,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="40" customHeight="1">
+    <row r="180" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A180" s="16" t="s">
         <v>114</v>
       </c>
@@ -19765,7 +19681,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="40" customHeight="1">
+    <row r="181" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A181" s="16" t="s">
         <v>114</v>
       </c>
@@ -19785,7 +19701,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="40" customHeight="1">
+    <row r="182" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A182" s="16" t="s">
         <v>114</v>
       </c>
@@ -19805,7 +19721,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="40" customHeight="1">
+    <row r="183" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A183" s="16" t="s">
         <v>114</v>
       </c>
@@ -19825,7 +19741,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="40" customHeight="1">
+    <row r="184" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A184" s="16" t="s">
         <v>114</v>
       </c>
@@ -19845,7 +19761,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="40" customHeight="1">
+    <row r="185" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A185" s="16" t="s">
         <v>114</v>
       </c>
@@ -19865,7 +19781,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="40" customHeight="1">
+    <row r="186" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A186" s="16" t="s">
         <v>114</v>
       </c>
@@ -19885,7 +19801,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="40" customHeight="1">
+    <row r="187" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A187" s="16" t="s">
         <v>114</v>
       </c>
@@ -19905,7 +19821,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="40" customHeight="1">
+    <row r="188" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A188" s="16" t="s">
         <v>115</v>
       </c>
@@ -19925,7 +19841,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="40" customHeight="1">
+    <row r="189" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A189" s="16" t="s">
         <v>115</v>
       </c>
@@ -19945,7 +19861,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="40" customHeight="1">
+    <row r="190" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A190" s="16" t="s">
         <v>115</v>
       </c>
@@ -19965,7 +19881,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="40" customHeight="1">
+    <row r="191" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A191" s="16" t="s">
         <v>115</v>
       </c>
@@ -19985,7 +19901,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="40" customHeight="1">
+    <row r="192" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A192" s="16" t="s">
         <v>115</v>
       </c>
@@ -20005,7 +19921,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="40" customHeight="1">
+    <row r="193" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A193" s="16" t="s">
         <v>115</v>
       </c>
@@ -20025,7 +19941,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="40" customHeight="1">
+    <row r="194" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A194" s="16" t="s">
         <v>115</v>
       </c>
@@ -20045,7 +19961,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="40" customHeight="1">
+    <row r="195" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A195" s="16" t="s">
         <v>115</v>
       </c>
@@ -20065,7 +19981,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="40" customHeight="1">
+    <row r="196" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A196" s="16" t="s">
         <v>115</v>
       </c>
@@ -20085,7 +20001,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="40" customHeight="1">
+    <row r="197" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A197" s="16" t="s">
         <v>115</v>
       </c>
@@ -20105,7 +20021,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="40" customHeight="1">
+    <row r="198" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A198" s="16" t="s">
         <v>115</v>
       </c>
@@ -20125,7 +20041,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="40" customHeight="1">
+    <row r="199" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A199" s="16" t="s">
         <v>115</v>
       </c>
@@ -20145,7 +20061,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="40" customHeight="1">
+    <row r="200" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A200" s="16" t="s">
         <v>115</v>
       </c>
@@ -20165,7 +20081,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="40" customHeight="1">
+    <row r="201" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A201" s="16" t="s">
         <v>115</v>
       </c>
@@ -20185,7 +20101,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="40" customHeight="1">
+    <row r="202" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A202" s="16" t="s">
         <v>115</v>
       </c>
@@ -20205,7 +20121,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="40" customHeight="1">
+    <row r="203" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A203" s="16" t="s">
         <v>115</v>
       </c>
@@ -20225,7 +20141,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="40" customHeight="1">
+    <row r="204" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A204" s="16" t="s">
         <v>115</v>
       </c>
@@ -20245,7 +20161,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="40" customHeight="1">
+    <row r="205" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A205" s="16" t="s">
         <v>115</v>
       </c>
@@ -20265,7 +20181,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="40" customHeight="1">
+    <row r="206" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A206" s="16" t="s">
         <v>115</v>
       </c>
@@ -20285,7 +20201,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="40" customHeight="1">
+    <row r="207" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A207" s="16" t="s">
         <v>116</v>
       </c>
@@ -20305,7 +20221,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="40" customHeight="1">
+    <row r="208" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A208" s="16" t="s">
         <v>116</v>
       </c>
@@ -20325,7 +20241,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="40" customHeight="1">
+    <row r="209" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A209" s="16" t="s">
         <v>116</v>
       </c>
@@ -20345,7 +20261,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="40" customHeight="1">
+    <row r="210" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A210" s="16" t="s">
         <v>116</v>
       </c>
@@ -20365,7 +20281,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="40" customHeight="1">
+    <row r="211" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A211" s="16" t="s">
         <v>116</v>
       </c>
@@ -20385,7 +20301,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="40" customHeight="1">
+    <row r="212" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A212" s="16" t="s">
         <v>116</v>
       </c>
@@ -20405,7 +20321,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="40" customHeight="1">
+    <row r="213" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A213" s="16" t="s">
         <v>116</v>
       </c>
@@ -20425,7 +20341,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="40" customHeight="1">
+    <row r="214" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A214" s="16" t="s">
         <v>116</v>
       </c>
@@ -20445,7 +20361,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="40" customHeight="1">
+    <row r="215" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A215" s="16" t="s">
         <v>116</v>
       </c>
@@ -20465,7 +20381,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="216" spans="1:6" ht="40" customHeight="1">
+    <row r="216" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A216" s="16" t="s">
         <v>116</v>
       </c>
@@ -20485,7 +20401,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="217" spans="1:6" ht="40" customHeight="1">
+    <row r="217" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A217" s="16" t="s">
         <v>116</v>
       </c>
@@ -20505,7 +20421,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="40" customHeight="1">
+    <row r="218" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A218" s="16" t="s">
         <v>116</v>
       </c>
@@ -20525,7 +20441,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="40" customHeight="1">
+    <row r="219" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A219" s="16" t="s">
         <v>116</v>
       </c>
@@ -20545,7 +20461,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="40" customHeight="1">
+    <row r="220" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A220" s="16" t="s">
         <v>116</v>
       </c>
@@ -20565,7 +20481,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="221" spans="1:6" ht="40" customHeight="1">
+    <row r="221" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A221" s="25" t="s">
         <v>116</v>
       </c>
@@ -20585,7 +20501,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="40" customHeight="1">
+    <row r="222" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A222" s="42"/>
       <c r="B222" s="42"/>
       <c r="C222" s="43"/>
@@ -20593,7 +20509,7 @@
       <c r="E222" s="43"/>
       <c r="F222" s="28"/>
     </row>
-    <row r="223" spans="1:6" ht="40" customHeight="1">
+    <row r="223" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A223" s="42"/>
       <c r="B223" s="42"/>
       <c r="C223" s="43"/>
@@ -20601,7 +20517,7 @@
       <c r="E223" s="43"/>
       <c r="F223" s="28"/>
     </row>
-    <row r="224" spans="1:6" ht="40" customHeight="1">
+    <row r="224" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A224" s="42"/>
       <c r="B224" s="42"/>
       <c r="C224" s="43"/>
@@ -20609,7 +20525,7 @@
       <c r="E224" s="43"/>
       <c r="F224" s="28"/>
     </row>
-    <row r="225" spans="1:16" ht="40" customHeight="1">
+    <row r="225" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A225" s="42"/>
       <c r="B225" s="42"/>
       <c r="C225" s="43"/>
@@ -20617,7 +20533,7 @@
       <c r="E225" s="43"/>
       <c r="F225" s="28"/>
     </row>
-    <row r="226" spans="1:16" ht="40" customHeight="1">
+    <row r="226" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A226" s="42"/>
       <c r="B226" s="42"/>
       <c r="C226" s="43"/>
@@ -20625,7 +20541,7 @@
       <c r="E226" s="43"/>
       <c r="F226" s="28"/>
     </row>
-    <row r="227" spans="1:16" ht="40" customHeight="1">
+    <row r="227" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A227" s="42"/>
       <c r="B227" s="42"/>
       <c r="C227" s="43"/>
@@ -20633,7 +20549,7 @@
       <c r="E227" s="43"/>
       <c r="F227" s="28"/>
     </row>
-    <row r="228" spans="1:16" ht="40" customHeight="1">
+    <row r="228" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A228" s="42"/>
       <c r="B228" s="42"/>
       <c r="C228" s="43"/>
@@ -20641,7 +20557,7 @@
       <c r="E228" s="43"/>
       <c r="F228" s="28"/>
     </row>
-    <row r="229" spans="1:16" ht="40" customHeight="1">
+    <row r="229" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A229" s="42"/>
       <c r="B229" s="42"/>
       <c r="C229" s="43"/>
@@ -20649,7 +20565,7 @@
       <c r="E229" s="43"/>
       <c r="F229" s="28"/>
     </row>
-    <row r="230" spans="1:16" ht="40" customHeight="1">
+    <row r="230" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A230" s="42"/>
       <c r="B230" s="42"/>
       <c r="C230" s="43"/>
@@ -20657,7 +20573,7 @@
       <c r="E230" s="43"/>
       <c r="F230" s="28"/>
     </row>
-    <row r="231" spans="1:16" ht="40" customHeight="1">
+    <row r="231" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A231" s="42"/>
       <c r="B231" s="42"/>
       <c r="C231" s="43"/>
@@ -20665,7 +20581,7 @@
       <c r="E231" s="43"/>
       <c r="F231" s="28"/>
     </row>
-    <row r="232" spans="1:16" ht="40" customHeight="1">
+    <row r="232" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A232" s="42"/>
       <c r="B232" s="42"/>
       <c r="C232" s="43"/>
@@ -20673,7 +20589,7 @@
       <c r="E232" s="43"/>
       <c r="F232" s="28"/>
     </row>
-    <row r="233" spans="1:16" ht="40" customHeight="1">
+    <row r="233" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A233" s="42"/>
       <c r="B233" s="42"/>
       <c r="C233" s="43"/>
@@ -20681,7 +20597,7 @@
       <c r="E233" s="43"/>
       <c r="F233" s="28"/>
     </row>
-    <row r="234" spans="1:16" ht="40" customHeight="1">
+    <row r="234" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A234" s="42"/>
       <c r="B234" s="42"/>
       <c r="C234" s="43"/>
@@ -20689,7 +20605,7 @@
       <c r="E234" s="43"/>
       <c r="F234" s="28"/>
     </row>
-    <row r="235" spans="1:16" ht="40" customHeight="1">
+    <row r="235" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A235" s="42"/>
       <c r="B235" s="42"/>
       <c r="C235" s="43"/>
@@ -20697,7 +20613,7 @@
       <c r="E235" s="43"/>
       <c r="F235" s="28"/>
     </row>
-    <row r="236" spans="1:16" ht="40" customHeight="1">
+    <row r="236" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A236" s="42"/>
       <c r="B236" s="42"/>
       <c r="C236" s="43"/>
@@ -20705,7 +20621,7 @@
       <c r="E236" s="43"/>
       <c r="F236" s="28"/>
     </row>
-    <row r="237" spans="1:16" ht="40" customHeight="1">
+    <row r="237" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A237" s="42"/>
       <c r="B237" s="42"/>
       <c r="C237" s="43"/>
@@ -20714,7 +20630,7 @@
       <c r="F237" s="28"/>
       <c r="P237" s="8"/>
     </row>
-    <row r="238" spans="1:16" ht="40" customHeight="1">
+    <row r="238" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A238" s="42"/>
       <c r="B238" s="42"/>
       <c r="C238" s="43"/>
@@ -20723,7 +20639,7 @@
       <c r="F238" s="28"/>
       <c r="L238" s="7"/>
     </row>
-    <row r="239" spans="1:16" ht="40" customHeight="1">
+    <row r="239" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A239" s="44"/>
       <c r="B239" s="42"/>
       <c r="C239" s="43"/>
@@ -20731,7 +20647,7 @@
       <c r="E239" s="43"/>
       <c r="F239" s="28"/>
     </row>
-    <row r="240" spans="1:16" ht="40" customHeight="1">
+    <row r="240" spans="1:16" ht="39.950000000000003" customHeight="1">
       <c r="A240" s="28"/>
       <c r="B240" s="28"/>
       <c r="C240" s="29"/>
@@ -20739,7 +20655,7 @@
       <c r="E240" s="29"/>
       <c r="F240" s="28"/>
     </row>
-    <row r="241" spans="1:6" ht="40" customHeight="1">
+    <row r="241" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A241" s="28"/>
       <c r="B241" s="28"/>
       <c r="C241" s="29"/>
@@ -20747,7 +20663,7 @@
       <c r="E241" s="29"/>
       <c r="F241" s="28"/>
     </row>
-    <row r="242" spans="1:6" ht="40" customHeight="1">
+    <row r="242" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A242" s="28"/>
       <c r="B242" s="28"/>
       <c r="C242" s="29"/>
@@ -20755,7 +20671,7 @@
       <c r="E242" s="29"/>
       <c r="F242" s="28"/>
     </row>
-    <row r="243" spans="1:6" ht="40" customHeight="1">
+    <row r="243" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A243" s="28"/>
       <c r="B243" s="28"/>
       <c r="C243" s="29"/>
@@ -20763,7 +20679,7 @@
       <c r="E243" s="29"/>
       <c r="F243" s="28"/>
     </row>
-    <row r="244" spans="1:6" ht="40" customHeight="1">
+    <row r="244" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A244" s="28"/>
       <c r="B244" s="28"/>
       <c r="C244" s="29"/>
@@ -20771,7 +20687,7 @@
       <c r="E244" s="29"/>
       <c r="F244" s="28"/>
     </row>
-    <row r="245" spans="1:6" ht="40" customHeight="1">
+    <row r="245" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A245" s="28"/>
       <c r="B245" s="28"/>
       <c r="C245" s="29"/>
@@ -20779,7 +20695,7 @@
       <c r="E245" s="29"/>
       <c r="F245" s="28"/>
     </row>
-    <row r="246" spans="1:6" ht="40" customHeight="1">
+    <row r="246" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A246" s="28"/>
       <c r="B246" s="28"/>
       <c r="C246" s="30"/>
@@ -20787,7 +20703,7 @@
       <c r="E246" s="29"/>
       <c r="F246" s="28"/>
     </row>
-    <row r="247" spans="1:6" ht="40" customHeight="1">
+    <row r="247" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A247" s="28"/>
       <c r="B247" s="28"/>
       <c r="C247" s="29"/>
@@ -20795,7 +20711,7 @@
       <c r="E247" s="29"/>
       <c r="F247" s="28"/>
     </row>
-    <row r="248" spans="1:6" ht="40" customHeight="1">
+    <row r="248" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A248" s="28"/>
       <c r="B248" s="28"/>
       <c r="C248" s="29"/>
@@ -20803,7 +20719,7 @@
       <c r="E248" s="29"/>
       <c r="F248" s="28"/>
     </row>
-    <row r="249" spans="1:6" ht="40" customHeight="1">
+    <row r="249" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A249" s="28"/>
       <c r="B249" s="28"/>
       <c r="C249" s="29"/>
@@ -20811,7 +20727,7 @@
       <c r="E249" s="29"/>
       <c r="F249" s="28"/>
     </row>
-    <row r="250" spans="1:6" ht="40" customHeight="1">
+    <row r="250" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A250" s="28"/>
       <c r="B250" s="28"/>
       <c r="C250" s="30"/>
@@ -20819,7 +20735,7 @@
       <c r="E250" s="29"/>
       <c r="F250" s="28"/>
     </row>
-    <row r="251" spans="1:6" ht="40" customHeight="1">
+    <row r="251" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A251" s="28"/>
       <c r="B251" s="28"/>
       <c r="C251" s="29"/>
@@ -20827,7 +20743,7 @@
       <c r="E251" s="29"/>
       <c r="F251" s="28"/>
     </row>
-    <row r="252" spans="1:6" ht="40" customHeight="1">
+    <row r="252" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A252" s="28"/>
       <c r="B252" s="28"/>
       <c r="C252" s="29"/>
@@ -20835,7 +20751,7 @@
       <c r="E252" s="29"/>
       <c r="F252" s="28"/>
     </row>
-    <row r="253" spans="1:6" ht="40" customHeight="1">
+    <row r="253" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A253" s="28"/>
       <c r="B253" s="28"/>
       <c r="C253" s="29"/>
@@ -20843,7 +20759,7 @@
       <c r="E253" s="29"/>
       <c r="F253" s="28"/>
     </row>
-    <row r="254" spans="1:6" ht="40" customHeight="1">
+    <row r="254" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A254" s="28"/>
       <c r="B254" s="28"/>
       <c r="C254" s="30"/>
@@ -20851,7 +20767,7 @@
       <c r="E254" s="29"/>
       <c r="F254" s="28"/>
     </row>
-    <row r="255" spans="1:6" ht="40" customHeight="1">
+    <row r="255" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A255" s="28"/>
       <c r="B255" s="28"/>
       <c r="C255" s="29"/>
@@ -20859,7 +20775,7 @@
       <c r="E255" s="29"/>
       <c r="F255" s="28"/>
     </row>
-    <row r="256" spans="1:6" ht="40" customHeight="1">
+    <row r="256" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A256" s="28"/>
       <c r="B256" s="28"/>
       <c r="C256" s="30"/>
@@ -20867,7 +20783,7 @@
       <c r="E256" s="29"/>
       <c r="F256" s="28"/>
     </row>
-    <row r="257" spans="1:6" ht="40" customHeight="1">
+    <row r="257" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A257" s="28"/>
       <c r="B257" s="28"/>
       <c r="C257" s="29"/>
@@ -20875,7 +20791,7 @@
       <c r="E257" s="30"/>
       <c r="F257" s="28"/>
     </row>
-    <row r="258" spans="1:6" ht="40" customHeight="1">
+    <row r="258" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A258" s="28"/>
       <c r="B258" s="28"/>
       <c r="C258" s="30"/>
@@ -20883,7 +20799,7 @@
       <c r="E258" s="29"/>
       <c r="F258" s="28"/>
     </row>
-    <row r="259" spans="1:6" ht="40" customHeight="1">
+    <row r="259" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A259" s="28"/>
       <c r="B259" s="28"/>
       <c r="C259" s="29"/>
@@ -20891,7 +20807,7 @@
       <c r="E259" s="29"/>
       <c r="F259" s="28"/>
     </row>
-    <row r="260" spans="1:6" ht="40" customHeight="1">
+    <row r="260" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A260" s="28"/>
       <c r="B260" s="28"/>
       <c r="C260" s="30"/>
@@ -20899,7 +20815,7 @@
       <c r="E260" s="29"/>
       <c r="F260" s="28"/>
     </row>
-    <row r="261" spans="1:6" ht="40" customHeight="1">
+    <row r="261" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A261" s="28"/>
       <c r="B261" s="28"/>
       <c r="C261" s="29"/>
@@ -20907,7 +20823,7 @@
       <c r="E261" s="30"/>
       <c r="F261" s="28"/>
     </row>
-    <row r="262" spans="1:6" ht="40" customHeight="1">
+    <row r="262" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A262" s="28"/>
       <c r="B262" s="28"/>
       <c r="C262" s="29"/>
@@ -20915,7 +20831,7 @@
       <c r="E262" s="29"/>
       <c r="F262" s="28"/>
     </row>
-    <row r="263" spans="1:6" ht="40" customHeight="1">
+    <row r="263" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A263" s="28"/>
       <c r="B263" s="28"/>
       <c r="C263" s="30"/>
@@ -20923,7 +20839,7 @@
       <c r="E263" s="29"/>
       <c r="F263" s="28"/>
     </row>
-    <row r="264" spans="1:6" ht="40" customHeight="1">
+    <row r="264" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A264" s="28"/>
       <c r="B264" s="28"/>
       <c r="C264" s="29"/>
@@ -20931,7 +20847,7 @@
       <c r="E264" s="29"/>
       <c r="F264" s="28"/>
     </row>
-    <row r="265" spans="1:6" ht="40" customHeight="1">
+    <row r="265" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A265" s="28"/>
       <c r="B265" s="28"/>
       <c r="C265" s="29"/>
@@ -20939,7 +20855,7 @@
       <c r="E265" s="29"/>
       <c r="F265" s="28"/>
     </row>
-    <row r="266" spans="1:6" ht="40" customHeight="1">
+    <row r="266" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A266" s="28"/>
       <c r="B266" s="28"/>
       <c r="C266" s="29"/>
@@ -20947,7 +20863,7 @@
       <c r="E266" s="29"/>
       <c r="F266" s="28"/>
     </row>
-    <row r="267" spans="1:6" ht="40" customHeight="1">
+    <row r="267" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A267" s="28"/>
       <c r="B267" s="28"/>
       <c r="C267" s="30"/>
@@ -20955,7 +20871,7 @@
       <c r="E267" s="29"/>
       <c r="F267" s="28"/>
     </row>
-    <row r="268" spans="1:6" ht="40" customHeight="1">
+    <row r="268" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A268" s="28"/>
       <c r="B268" s="28"/>
       <c r="C268" s="29"/>
@@ -20963,7 +20879,7 @@
       <c r="E268" s="29"/>
       <c r="F268" s="28"/>
     </row>
-    <row r="269" spans="1:6" ht="40" customHeight="1">
+    <row r="269" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A269" s="28"/>
       <c r="B269" s="28"/>
       <c r="C269" s="29"/>
@@ -20971,7 +20887,7 @@
       <c r="E269" s="29"/>
       <c r="F269" s="28"/>
     </row>
-    <row r="270" spans="1:6" ht="40" customHeight="1">
+    <row r="270" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A270" s="28"/>
       <c r="B270" s="28"/>
       <c r="C270" s="29"/>
@@ -20979,7 +20895,7 @@
       <c r="E270" s="29"/>
       <c r="F270" s="28"/>
     </row>
-    <row r="271" spans="1:6" ht="40" customHeight="1">
+    <row r="271" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A271" s="28"/>
       <c r="B271" s="28"/>
       <c r="C271" s="30"/>
@@ -20987,7 +20903,7 @@
       <c r="E271" s="29"/>
       <c r="F271" s="28"/>
     </row>
-    <row r="272" spans="1:6" ht="40" customHeight="1">
+    <row r="272" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A272" s="28"/>
       <c r="B272" s="28"/>
       <c r="C272" s="29"/>
@@ -20995,7 +20911,7 @@
       <c r="E272" s="29"/>
       <c r="F272" s="28"/>
     </row>
-    <row r="273" spans="1:6" ht="40" customHeight="1">
+    <row r="273" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A273" s="28"/>
       <c r="B273" s="28"/>
       <c r="C273" s="29"/>
@@ -21003,7 +20919,7 @@
       <c r="E273" s="29"/>
       <c r="F273" s="28"/>
     </row>
-    <row r="274" spans="1:6" ht="40" customHeight="1">
+    <row r="274" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A274" s="28"/>
       <c r="B274" s="28"/>
       <c r="C274" s="29"/>
@@ -21011,7 +20927,7 @@
       <c r="E274" s="29"/>
       <c r="F274" s="28"/>
     </row>
-    <row r="275" spans="1:6" ht="40" customHeight="1">
+    <row r="275" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A275" s="28"/>
       <c r="B275" s="28"/>
       <c r="C275" s="30"/>
@@ -21019,7 +20935,7 @@
       <c r="E275" s="29"/>
       <c r="F275" s="28"/>
     </row>
-    <row r="276" spans="1:6" ht="40" customHeight="1">
+    <row r="276" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A276" s="28"/>
       <c r="B276" s="28"/>
       <c r="C276" s="29"/>
@@ -21027,7 +20943,7 @@
       <c r="E276" s="29"/>
       <c r="F276" s="28"/>
     </row>
-    <row r="277" spans="1:6" ht="40" customHeight="1">
+    <row r="277" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A277" s="28"/>
       <c r="B277" s="28"/>
       <c r="C277" s="29"/>
@@ -21035,7 +20951,7 @@
       <c r="E277" s="29"/>
       <c r="F277" s="28"/>
     </row>
-    <row r="278" spans="1:6" ht="40" customHeight="1">
+    <row r="278" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A278" s="28"/>
       <c r="B278" s="28"/>
       <c r="C278" s="30"/>
@@ -21043,7 +20959,7 @@
       <c r="E278" s="30"/>
       <c r="F278" s="28"/>
     </row>
-    <row r="279" spans="1:6" ht="40" customHeight="1">
+    <row r="279" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A279" s="28"/>
       <c r="B279" s="28"/>
       <c r="C279" s="30"/>
@@ -21051,7 +20967,7 @@
       <c r="E279" s="30"/>
       <c r="F279" s="28"/>
     </row>
-    <row r="280" spans="1:6" ht="40" customHeight="1">
+    <row r="280" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A280" s="28"/>
       <c r="B280" s="28"/>
       <c r="C280" s="30"/>
@@ -21059,7 +20975,7 @@
       <c r="E280" s="30"/>
       <c r="F280" s="28"/>
     </row>
-    <row r="281" spans="1:6" ht="40" customHeight="1">
+    <row r="281" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A281" s="28"/>
       <c r="B281" s="28"/>
       <c r="C281" s="29"/>
@@ -21067,7 +20983,7 @@
       <c r="E281" s="29"/>
       <c r="F281" s="28"/>
     </row>
-    <row r="282" spans="1:6" ht="40" customHeight="1">
+    <row r="282" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A282" s="28"/>
       <c r="B282" s="28"/>
       <c r="C282" s="30"/>
@@ -21075,7 +20991,7 @@
       <c r="E282" s="30"/>
       <c r="F282" s="28"/>
     </row>
-    <row r="283" spans="1:6" ht="40" customHeight="1">
+    <row r="283" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A283" s="28"/>
       <c r="B283" s="28"/>
       <c r="C283" s="30"/>
@@ -21083,7 +20999,7 @@
       <c r="E283" s="30"/>
       <c r="F283" s="28"/>
     </row>
-    <row r="284" spans="1:6" ht="40" customHeight="1">
+    <row r="284" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A284" s="28"/>
       <c r="B284" s="28"/>
       <c r="C284" s="29"/>
@@ -21091,7 +21007,7 @@
       <c r="E284" s="29"/>
       <c r="F284" s="28"/>
     </row>
-    <row r="285" spans="1:6" ht="40" customHeight="1">
+    <row r="285" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A285" s="28"/>
       <c r="B285" s="28"/>
       <c r="C285" s="29"/>
@@ -21099,7 +21015,7 @@
       <c r="E285" s="29"/>
       <c r="F285" s="28"/>
     </row>
-    <row r="286" spans="1:6" ht="40" customHeight="1">
+    <row r="286" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A286" s="28"/>
       <c r="B286" s="28"/>
       <c r="C286" s="30"/>
@@ -21107,7 +21023,7 @@
       <c r="E286" s="29"/>
       <c r="F286" s="28"/>
     </row>
-    <row r="287" spans="1:6" ht="40" customHeight="1">
+    <row r="287" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A287" s="28"/>
       <c r="B287" s="28"/>
       <c r="C287" s="30"/>
@@ -21115,7 +21031,7 @@
       <c r="E287" s="29"/>
       <c r="F287" s="28"/>
     </row>
-    <row r="288" spans="1:6" ht="40" customHeight="1">
+    <row r="288" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A288" s="28"/>
       <c r="B288" s="28"/>
       <c r="C288" s="30"/>
@@ -21123,7 +21039,7 @@
       <c r="E288" s="29"/>
       <c r="F288" s="28"/>
     </row>
-    <row r="289" spans="1:6" ht="40" customHeight="1">
+    <row r="289" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A289" s="28"/>
       <c r="B289" s="28"/>
       <c r="C289" s="29"/>
@@ -21131,7 +21047,7 @@
       <c r="E289" s="29"/>
       <c r="F289" s="28"/>
     </row>
-    <row r="290" spans="1:6" ht="40" customHeight="1">
+    <row r="290" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A290" s="28"/>
       <c r="B290" s="28"/>
       <c r="C290" s="30"/>
@@ -21139,7 +21055,7 @@
       <c r="E290" s="30"/>
       <c r="F290" s="28"/>
     </row>
-    <row r="291" spans="1:6" ht="40" customHeight="1">
+    <row r="291" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A291" s="28"/>
       <c r="B291" s="28"/>
       <c r="C291" s="30"/>
@@ -21147,7 +21063,7 @@
       <c r="E291" s="30"/>
       <c r="F291" s="28"/>
     </row>
-    <row r="292" spans="1:6" ht="40" customHeight="1">
+    <row r="292" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A292" s="28"/>
       <c r="B292" s="28"/>
       <c r="C292" s="29"/>
@@ -21155,7 +21071,7 @@
       <c r="E292" s="29"/>
       <c r="F292" s="28"/>
     </row>
-    <row r="293" spans="1:6" ht="40" customHeight="1">
+    <row r="293" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A293" s="28"/>
       <c r="B293" s="28"/>
       <c r="C293" s="29"/>
@@ -21163,7 +21079,7 @@
       <c r="E293" s="29"/>
       <c r="F293" s="28"/>
     </row>
-    <row r="294" spans="1:6" ht="40" customHeight="1">
+    <row r="294" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A294" s="28"/>
       <c r="B294" s="28"/>
       <c r="C294" s="30"/>
@@ -21171,7 +21087,7 @@
       <c r="E294" s="29"/>
       <c r="F294" s="28"/>
     </row>
-    <row r="295" spans="1:6" ht="40" customHeight="1">
+    <row r="295" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A295" s="28"/>
       <c r="B295" s="28"/>
       <c r="C295" s="30"/>
@@ -21179,7 +21095,7 @@
       <c r="E295" s="29"/>
       <c r="F295" s="28"/>
     </row>
-    <row r="296" spans="1:6" ht="40" customHeight="1">
+    <row r="296" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A296" s="28"/>
       <c r="B296" s="28"/>
       <c r="C296" s="30"/>
@@ -21187,7 +21103,7 @@
       <c r="E296" s="29"/>
       <c r="F296" s="28"/>
     </row>
-    <row r="297" spans="1:6" ht="40" customHeight="1">
+    <row r="297" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A297" s="28"/>
       <c r="B297" s="28"/>
       <c r="C297" s="29"/>
@@ -21195,7 +21111,7 @@
       <c r="E297" s="29"/>
       <c r="F297" s="28"/>
     </row>
-    <row r="298" spans="1:6" ht="40" customHeight="1">
+    <row r="298" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A298" s="28"/>
       <c r="B298" s="28"/>
       <c r="C298" s="30"/>
@@ -21203,7 +21119,7 @@
       <c r="E298" s="30"/>
       <c r="F298" s="28"/>
     </row>
-    <row r="299" spans="1:6" ht="40" customHeight="1">
+    <row r="299" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A299" s="28"/>
       <c r="B299" s="28"/>
       <c r="C299" s="30"/>
@@ -21211,7 +21127,7 @@
       <c r="E299" s="30"/>
       <c r="F299" s="28"/>
     </row>
-    <row r="300" spans="1:6" ht="40" customHeight="1">
+    <row r="300" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A300" s="28"/>
       <c r="B300" s="28"/>
       <c r="C300" s="30"/>
@@ -21265,11 +21181,11 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="F5:F221">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",F5)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",F5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH("Fail",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21281,1977 +21197,1971 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EB1D2A9-53E8-4C1E-9383-87BD574595B3}">
   <dimension ref="A1:O60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15" style="45" customWidth="1"/>
     <col min="3" max="3" width="12" style="45" customWidth="1"/>
     <col min="4" max="4" width="18" style="45" customWidth="1"/>
     <col min="5" max="5" width="11" style="45" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="45" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="45" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="45" customWidth="1"/>
     <col min="8" max="8" width="4" style="45" customWidth="1"/>
-    <col min="9" max="11" width="13" style="45" customWidth="1"/>
-    <col min="12" max="15" width="14" style="45" customWidth="1"/>
-    <col min="16" max="16384" width="9.1640625" style="45"/>
+    <col min="9" max="10" width="13" style="45" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" style="45" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" style="45" customWidth="1"/>
+    <col min="13" max="15" width="14" style="45" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="34" customHeight="1">
-      <c r="A1" s="67" t="s">
+    <row r="1" spans="1:15" ht="33.950000000000003" customHeight="1">
+      <c r="A1" s="59" t="s">
         <v>749</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="60" t="s">
         <v>750</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
     </row>
     <row r="3" spans="1:15" ht="21" customHeight="1">
-      <c r="A3" s="91"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="91"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
     </row>
     <row r="4" spans="1:15" ht="21" customHeight="1">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="61" t="s">
         <v>751</v>
       </c>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69" t="s">
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="62" t="s">
         <v>752</v>
       </c>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="70" t="s">
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="63" t="s">
         <v>753</v>
       </c>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="71" t="s">
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="64" t="s">
         <v>754</v>
       </c>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="72" t="s">
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="65" t="s">
         <v>755</v>
       </c>
-      <c r="N4" s="72"/>
-      <c r="O4" s="72"/>
-    </row>
-    <row r="5" spans="1:15" ht="26" customHeight="1">
-      <c r="A5" s="82">
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+    </row>
+    <row r="5" spans="1:15" ht="26.1" customHeight="1">
+      <c r="A5" s="67">
         <f>COUNTA($A$41:$A$55)</f>
         <v>15</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82">
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67">
         <f>SUM($E$41:$E$55)</f>
         <v>217</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82">
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67">
         <f>SUM($F$41:$F$55)</f>
         <v>217</v>
       </c>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82">
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67">
         <f>SUM($G$41:$G$55)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="84">
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="68">
         <f>IFERROR(SUM($F$41:$F$55)/SUM($E$41:$E$55),0)</f>
         <v>1</v>
       </c>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-    </row>
-    <row r="6" spans="1:15" ht="26" customHeight="1">
-      <c r="A6" s="82"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="84"/>
-      <c r="O6" s="84"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+    </row>
+    <row r="6" spans="1:15" ht="26.1" customHeight="1">
+      <c r="A6" s="67"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
     </row>
     <row r="7" spans="1:15" ht="21" customHeight="1">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="66" t="s">
         <v>756</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66" t="s">
         <v>757</v>
       </c>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83" t="s">
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66" t="s">
         <v>758</v>
       </c>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83" t="s">
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66" t="s">
         <v>759</v>
       </c>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83" t="s">
+      <c r="K7" s="66"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="66" t="s">
         <v>760</v>
       </c>
-      <c r="N7" s="83"/>
-      <c r="O7" s="83"/>
+      <c r="N7" s="66"/>
+      <c r="O7" s="66"/>
     </row>
     <row r="8" spans="1:15" ht="21" customHeight="1">
-      <c r="A8" s="76"/>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
-      <c r="J8" s="76"/>
-      <c r="K8" s="76"/>
-      <c r="L8" s="76"/>
-      <c r="M8" s="76"/>
-      <c r="N8" s="76"/>
-      <c r="O8" s="76"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
     </row>
     <row r="9" spans="1:15" ht="21" customHeight="1">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="70" t="s">
         <v>761</v>
       </c>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="63" t="s">
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="71" t="s">
         <v>762</v>
       </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="64" t="s">
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="72" t="s">
         <v>763</v>
       </c>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="65" t="s">
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="73" t="s">
         <v>764</v>
       </c>
-      <c r="K9" s="65"/>
-      <c r="L9" s="65"/>
-      <c r="M9" s="66" t="s">
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="74" t="s">
         <v>765</v>
       </c>
-      <c r="N9" s="66"/>
-      <c r="O9" s="66"/>
-    </row>
-    <row r="10" spans="1:15" ht="26" customHeight="1">
-      <c r="A10" s="81" t="str">
+      <c r="N9" s="74"/>
+      <c r="O9" s="74"/>
+    </row>
+    <row r="10" spans="1:15" ht="26.1" customHeight="1">
+      <c r="A10" s="75" t="str">
         <f>COUNTIF($J$41:$J$55,"PASS")&amp;"/"&amp;COUNTA($A$41:$A$55)</f>
         <v>15/15</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81" t="str">
+      <c r="B10" s="75"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75" t="str">
         <f>COUNTIFS($C$41:$C$55,"Critical",$J$41:$J$55,"PASS")&amp;"/"&amp;COUNTIF($C$41:$C$55,"Critical")</f>
         <v>2/2</v>
       </c>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="82">
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="67">
         <f>COUNTIF($D$41:$D$55,"Semi-automatable")+COUNTIF($D$41:$D$55,"Candidate")</f>
         <v>9</v>
       </c>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82">
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67">
         <f>COUNTIF($D$41:$D$55,"Manual")</f>
         <v>6</v>
       </c>
-      <c r="K10" s="82"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="81" t="str">
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="75" t="str">
         <f>IF(SUM($G$41:$G$55)=0,"GREEN","CHECK")</f>
         <v>GREEN</v>
       </c>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
-    </row>
-    <row r="11" spans="1:15" ht="26" customHeight="1">
-      <c r="A11" s="81"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="81"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="75"/>
+    </row>
+    <row r="11" spans="1:15" ht="26.1" customHeight="1">
+      <c r="A11" s="75"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="75"/>
     </row>
     <row r="12" spans="1:15" ht="21" customHeight="1">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="66" t="s">
         <v>766</v>
       </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83" t="s">
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66" t="s">
         <v>767</v>
       </c>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83" t="s">
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66" t="s">
         <v>768</v>
       </c>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83" t="s">
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="66" t="s">
         <v>769</v>
       </c>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="83" t="s">
+      <c r="K12" s="66"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="66" t="s">
         <v>770</v>
       </c>
-      <c r="N12" s="83"/>
-      <c r="O12" s="83"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="66"/>
     </row>
     <row r="13" spans="1:15" ht="21" customHeight="1">
-      <c r="A13" s="76"/>
-      <c r="B13" s="76"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="76"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="76"/>
-      <c r="K13" s="76"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="76"/>
-      <c r="O13" s="76"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
     </row>
     <row r="14" spans="1:15" ht="21" customHeight="1">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="69" t="s">
         <v>771</v>
       </c>
-      <c r="B14" s="88"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="88"/>
-      <c r="E14" s="88"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="88" t="s">
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="69" t="s">
         <v>772</v>
       </c>
-      <c r="J14" s="88"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="88"/>
-      <c r="M14" s="88"/>
-      <c r="N14" s="88"/>
-      <c r="O14" s="88"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="69"/>
     </row>
     <row r="15" spans="1:15" ht="21" customHeight="1">
-      <c r="A15" s="95" t="s">
+      <c r="A15" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="95" t="s">
+      <c r="B15" s="58" t="s">
         <v>773</v>
       </c>
-      <c r="C15" s="95" t="s">
+      <c r="C15" s="58" t="s">
         <v>774</v>
       </c>
-      <c r="D15" s="95" t="s">
+      <c r="D15" s="58" t="s">
         <v>775</v>
       </c>
-      <c r="E15" s="95" t="s">
+      <c r="E15" s="58" t="s">
         <v>776</v>
       </c>
-      <c r="F15" s="95" t="s">
+      <c r="F15" s="58" t="s">
         <v>777</v>
       </c>
-      <c r="G15" s="95" t="s">
+      <c r="G15" s="58" t="s">
         <v>778</v>
       </c>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="89"/>
-      <c r="M15" s="89"/>
-      <c r="N15" s="89"/>
-      <c r="O15" s="89"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="55"/>
     </row>
     <row r="16" spans="1:15" ht="21" customHeight="1">
-      <c r="A16" s="78" t="s">
+      <c r="A16" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="79">
+      <c r="B16" s="51">
         <f t="shared" ref="B16:B24" si="0">COUNTIF($B$41:$B$55,A16)</f>
         <v>1</v>
       </c>
-      <c r="C16" s="79">
+      <c r="C16" s="51">
         <f t="shared" ref="C16:C24" si="1">SUMIF($B$41:$B$55,A16,$E$41:$E$55)</f>
         <v>15</v>
       </c>
-      <c r="D16" s="79">
+      <c r="D16" s="51">
         <f t="shared" ref="D16:D24" si="2">SUMIF($B$41:$B$55,A16,$F$41:$F$55)</f>
         <v>15</v>
       </c>
-      <c r="E16" s="79">
+      <c r="E16" s="51">
         <f t="shared" ref="E16:E24" si="3">SUMIF($B$41:$B$55,A16,$G$41:$G$55)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="80">
+      <c r="F16" s="52">
         <f t="shared" ref="F16:F24" si="4">IFERROR(D16/C16,0)</f>
         <v>1</v>
       </c>
-      <c r="G16" s="79">
+      <c r="G16" s="51">
         <f t="shared" ref="G16:G24" si="5">C16</f>
         <v>15</v>
       </c>
-      <c r="H16" s="76"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="76"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="76"/>
-      <c r="M16" s="76"/>
-      <c r="N16" s="76"/>
-      <c r="O16" s="76"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="49"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="49"/>
+      <c r="N16" s="49"/>
+      <c r="O16" s="49"/>
     </row>
     <row r="17" spans="1:15" ht="21" customHeight="1">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="79">
+      <c r="B17" s="51">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C17" s="79">
+      <c r="C17" s="51">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="D17" s="79">
+      <c r="D17" s="51">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="E17" s="79">
+      <c r="E17" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F17" s="80">
+      <c r="F17" s="52">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G17" s="79">
+      <c r="G17" s="51">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="H17" s="76"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="76"/>
-      <c r="K17" s="76"/>
-      <c r="L17" s="76"/>
-      <c r="M17" s="76"/>
-      <c r="N17" s="76"/>
-      <c r="O17" s="76"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="49"/>
     </row>
     <row r="18" spans="1:15" ht="21" customHeight="1">
-      <c r="A18" s="78" t="s">
+      <c r="A18" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="79">
+      <c r="B18" s="51">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C18" s="79">
+      <c r="C18" s="51">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="D18" s="79">
+      <c r="D18" s="51">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="E18" s="79">
+      <c r="E18" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F18" s="80">
+      <c r="F18" s="52">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G18" s="79">
+      <c r="G18" s="51">
         <f t="shared" si="5"/>
         <v>26</v>
       </c>
-      <c r="H18" s="76"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="76"/>
-      <c r="O18" s="76"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
+      <c r="N18" s="49"/>
+      <c r="O18" s="49"/>
     </row>
     <row r="19" spans="1:15" ht="21" customHeight="1">
-      <c r="A19" s="78" t="s">
+      <c r="A19" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="79">
+      <c r="B19" s="51">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C19" s="79">
+      <c r="C19" s="51">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="D19" s="79">
+      <c r="D19" s="51">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="E19" s="79">
+      <c r="E19" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F19" s="80">
+      <c r="F19" s="52">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G19" s="79">
+      <c r="G19" s="51">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="H19" s="76"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="76"/>
-      <c r="K19" s="76"/>
-      <c r="L19" s="76"/>
-      <c r="M19" s="76"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="76"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="49"/>
     </row>
     <row r="20" spans="1:15" ht="21" customHeight="1">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="79">
+      <c r="B20" s="51">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C20" s="79">
+      <c r="C20" s="51">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="D20" s="79">
+      <c r="D20" s="51">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="E20" s="79">
+      <c r="E20" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F20" s="80">
+      <c r="F20" s="52">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G20" s="79">
+      <c r="G20" s="51">
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="H20" s="76"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="76"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="76"/>
-      <c r="M20" s="76"/>
-      <c r="N20" s="76"/>
-      <c r="O20" s="76"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="49"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="49"/>
     </row>
     <row r="21" spans="1:15" ht="21" customHeight="1">
-      <c r="A21" s="78" t="s">
+      <c r="A21" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="79">
+      <c r="B21" s="51">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C21" s="79">
+      <c r="C21" s="51">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="D21" s="79">
+      <c r="D21" s="51">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="E21" s="79">
+      <c r="E21" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F21" s="80">
+      <c r="F21" s="52">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G21" s="79">
+      <c r="G21" s="51">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
-      <c r="H21" s="76"/>
-      <c r="I21" s="76"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="76"/>
-      <c r="M21" s="76"/>
-      <c r="N21" s="76"/>
-      <c r="O21" s="76"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
     </row>
     <row r="22" spans="1:15" ht="21" customHeight="1">
-      <c r="A22" s="78" t="s">
+      <c r="A22" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="79">
+      <c r="B22" s="51">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C22" s="79">
+      <c r="C22" s="51">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="D22" s="79">
+      <c r="D22" s="51">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="E22" s="79">
+      <c r="E22" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F22" s="80">
+      <c r="F22" s="52">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G22" s="79">
+      <c r="G22" s="51">
         <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="76"/>
-      <c r="O22" s="76"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="49"/>
+      <c r="O22" s="49"/>
     </row>
     <row r="23" spans="1:15" ht="21" customHeight="1">
-      <c r="A23" s="78" t="s">
+      <c r="A23" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="79">
+      <c r="B23" s="51">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C23" s="79">
+      <c r="C23" s="51">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="D23" s="79">
+      <c r="D23" s="51">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="E23" s="79">
+      <c r="E23" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F23" s="80">
+      <c r="F23" s="52">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G23" s="79">
+      <c r="G23" s="51">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
-      <c r="N23" s="76"/>
-      <c r="O23" s="76"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="49"/>
     </row>
     <row r="24" spans="1:15" ht="21" customHeight="1">
-      <c r="A24" s="78" t="s">
+      <c r="A24" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="79">
+      <c r="B24" s="51">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C24" s="79">
+      <c r="C24" s="51">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="D24" s="79">
+      <c r="D24" s="51">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="E24" s="79">
+      <c r="E24" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F24" s="80">
+      <c r="F24" s="52">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G24" s="79">
+      <c r="G24" s="51">
         <f t="shared" si="5"/>
         <v>29</v>
       </c>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="76"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="49"/>
+      <c r="O24" s="49"/>
     </row>
     <row r="25" spans="1:15" ht="21" customHeight="1">
-      <c r="A25" s="76"/>
-      <c r="B25" s="76"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="76"/>
-      <c r="M25" s="76"/>
-      <c r="N25" s="76"/>
-      <c r="O25" s="76"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="49"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="49"/>
     </row>
     <row r="26" spans="1:15" ht="21" customHeight="1">
-      <c r="A26" s="76"/>
-      <c r="B26" s="76"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="76"/>
-      <c r="K26" s="76"/>
-      <c r="L26" s="76"/>
-      <c r="M26" s="76"/>
-      <c r="N26" s="76"/>
-      <c r="O26" s="76"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
     </row>
     <row r="27" spans="1:15" ht="21" customHeight="1">
-      <c r="A27" s="76"/>
-      <c r="B27" s="76"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="76"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="76"/>
-      <c r="M27" s="76"/>
-      <c r="N27" s="76"/>
-      <c r="O27" s="76"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="49"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="49"/>
     </row>
     <row r="28" spans="1:15" ht="21" customHeight="1">
-      <c r="A28" s="92" t="s">
+      <c r="A28" s="76" t="s">
         <v>779</v>
       </c>
-      <c r="B28" s="93"/>
-      <c r="C28" s="93"/>
-      <c r="D28" s="93"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="94" t="s">
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="57" t="s">
         <v>780</v>
       </c>
-      <c r="G28" s="94"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="93" t="s">
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="77" t="s">
         <v>781</v>
       </c>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="93"/>
-      <c r="N28" s="93"/>
-      <c r="O28" s="93"/>
-    </row>
-    <row r="29" spans="1:15" ht="28" customHeight="1">
-      <c r="A29" s="95" t="s">
+      <c r="K28" s="77"/>
+      <c r="L28" s="77"/>
+      <c r="M28" s="77"/>
+      <c r="N28" s="77"/>
+      <c r="O28" s="77"/>
+    </row>
+    <row r="29" spans="1:15" ht="27.95" customHeight="1">
+      <c r="A29" s="58" t="s">
         <v>782</v>
       </c>
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="58" t="s">
         <v>773</v>
       </c>
-      <c r="C29" s="95" t="s">
+      <c r="C29" s="58" t="s">
         <v>783</v>
       </c>
-      <c r="D29" s="95" t="s">
+      <c r="D29" s="58" t="s">
         <v>784</v>
       </c>
-      <c r="E29" s="89"/>
-      <c r="F29" s="95" t="s">
+      <c r="E29" s="55"/>
+      <c r="F29" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="95" t="s">
+      <c r="G29" s="58" t="s">
         <v>773</v>
       </c>
-      <c r="H29" s="95" t="s">
+      <c r="H29" s="58" t="s">
         <v>785</v>
       </c>
-      <c r="I29" s="95" t="s">
+      <c r="I29" s="58" t="s">
         <v>777</v>
       </c>
-      <c r="J29" s="89"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="89"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="89"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="55"/>
     </row>
     <row r="30" spans="1:15" ht="21" customHeight="1">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="B30" s="79">
+      <c r="B30" s="51">
         <f>COUNTIF($D$41:$D$55,A30)</f>
         <v>1</v>
       </c>
-      <c r="C30" s="80">
+      <c r="C30" s="52">
         <f>IFERROR(B30/COUNTA($A$41:$A$55),0)</f>
         <v>6.6666666666666666E-2</v>
       </c>
-      <c r="D30" s="79">
+      <c r="D30" s="51">
         <f>B30</f>
         <v>1</v>
       </c>
-      <c r="E30" s="76"/>
-      <c r="F30" s="78" t="s">
+      <c r="E30" s="49"/>
+      <c r="F30" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="79">
+      <c r="G30" s="51">
         <f>COUNTIF($C$41:$C$55,F30)</f>
         <v>2</v>
       </c>
-      <c r="H30" s="79">
+      <c r="H30" s="51">
         <f>COUNTIFS($C$41:$C$55,F30,$J$41:$J$55,"PASS")</f>
         <v>2</v>
       </c>
-      <c r="I30" s="80">
+      <c r="I30" s="52">
         <f>IFERROR(H30/G30,0)</f>
         <v>1</v>
       </c>
-      <c r="J30" s="76"/>
-      <c r="K30" s="76"/>
-      <c r="L30" s="76"/>
-      <c r="M30" s="76"/>
-      <c r="N30" s="76"/>
-      <c r="O30" s="76"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="49"/>
+      <c r="L30" s="49"/>
+      <c r="M30" s="49"/>
+      <c r="N30" s="49"/>
+      <c r="O30" s="49"/>
     </row>
     <row r="31" spans="1:15" ht="21" customHeight="1">
-      <c r="A31" s="78" t="s">
+      <c r="A31" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="79">
+      <c r="B31" s="51">
         <f>COUNTIF($D$41:$D$55,A31)</f>
         <v>8</v>
       </c>
-      <c r="C31" s="80">
+      <c r="C31" s="52">
         <f>IFERROR(B31/COUNTA($A$41:$A$55),0)</f>
         <v>0.53333333333333333</v>
       </c>
-      <c r="D31" s="79">
+      <c r="D31" s="51">
         <f>B31</f>
         <v>8</v>
       </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="78" t="s">
+      <c r="E31" s="49"/>
+      <c r="F31" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="79">
+      <c r="G31" s="51">
         <f>COUNTIF($C$41:$C$55,F31)</f>
         <v>10</v>
       </c>
-      <c r="H31" s="79">
+      <c r="H31" s="51">
         <f>COUNTIFS($C$41:$C$55,F31,$J$41:$J$55,"PASS")</f>
         <v>10</v>
       </c>
-      <c r="I31" s="80">
+      <c r="I31" s="52">
         <f>IFERROR(H31/G31,0)</f>
         <v>1</v>
       </c>
-      <c r="J31" s="76"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="76"/>
-      <c r="M31" s="76"/>
-      <c r="N31" s="76"/>
-      <c r="O31" s="76"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="49"/>
+      <c r="M31" s="49"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="49"/>
     </row>
     <row r="32" spans="1:15" ht="21" customHeight="1">
-      <c r="A32" s="78" t="s">
+      <c r="A32" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="79">
+      <c r="B32" s="51">
         <f>COUNTIF($D$41:$D$55,A32)</f>
         <v>6</v>
       </c>
-      <c r="C32" s="80">
+      <c r="C32" s="52">
         <f>IFERROR(B32/COUNTA($A$41:$A$55),0)</f>
         <v>0.4</v>
       </c>
-      <c r="D32" s="79">
+      <c r="D32" s="51">
         <f>B32</f>
         <v>6</v>
       </c>
-      <c r="E32" s="76"/>
-      <c r="F32" s="78" t="s">
+      <c r="E32" s="49"/>
+      <c r="F32" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="79">
+      <c r="G32" s="51">
         <f>COUNTIF($C$41:$C$55,F32)</f>
         <v>3</v>
       </c>
-      <c r="H32" s="79">
+      <c r="H32" s="51">
         <f>COUNTIFS($C$41:$C$55,F32,$J$41:$J$55,"PASS")</f>
         <v>3</v>
       </c>
-      <c r="I32" s="80">
+      <c r="I32" s="52">
         <f>IFERROR(H32/G32,0)</f>
         <v>1</v>
       </c>
-      <c r="J32" s="76"/>
-      <c r="K32" s="76"/>
-      <c r="L32" s="76"/>
-      <c r="M32" s="76"/>
-      <c r="N32" s="76"/>
-      <c r="O32" s="76"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="49"/>
+      <c r="M32" s="49"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="49"/>
     </row>
     <row r="33" spans="1:15" ht="21" customHeight="1">
-      <c r="A33" s="76"/>
-      <c r="B33" s="76"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="76"/>
-      <c r="K33" s="76"/>
-      <c r="L33" s="76"/>
-      <c r="M33" s="76"/>
-      <c r="N33" s="76"/>
-      <c r="O33" s="76"/>
+      <c r="A33" s="49"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="49"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="49"/>
     </row>
     <row r="34" spans="1:15" ht="21" customHeight="1">
-      <c r="A34" s="92" t="s">
+      <c r="A34" s="76" t="s">
         <v>786</v>
       </c>
-      <c r="B34" s="93"/>
-      <c r="C34" s="93"/>
-      <c r="D34" s="93"/>
-      <c r="E34" s="93"/>
-      <c r="F34" s="93"/>
-      <c r="G34" s="93"/>
-      <c r="H34" s="93"/>
-      <c r="I34" s="93"/>
-      <c r="J34" s="91"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="91"/>
-      <c r="M34" s="91"/>
-      <c r="N34" s="91"/>
-      <c r="O34" s="91"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="56"/>
+      <c r="N34" s="56"/>
+      <c r="O34" s="56"/>
     </row>
     <row r="35" spans="1:15" ht="30" customHeight="1">
-      <c r="A35" s="86" t="s">
+      <c r="A35" s="53" t="s">
         <v>787</v>
       </c>
-      <c r="B35" s="85" t="s">
+      <c r="B35" s="79" t="s">
         <v>788</v>
       </c>
-      <c r="C35" s="85"/>
-      <c r="D35" s="85"/>
-      <c r="E35" s="85"/>
-      <c r="F35" s="85"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="85"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="76"/>
-      <c r="K35" s="76"/>
-      <c r="L35" s="76"/>
-      <c r="M35" s="76"/>
-      <c r="N35" s="76"/>
-      <c r="O35" s="76"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="49"/>
     </row>
     <row r="36" spans="1:15" ht="30" customHeight="1">
-      <c r="A36" s="87" t="s">
+      <c r="A36" s="54" t="s">
         <v>789</v>
       </c>
-      <c r="B36" s="85" t="s">
+      <c r="B36" s="79" t="s">
         <v>790</v>
       </c>
-      <c r="C36" s="85"/>
-      <c r="D36" s="85"/>
-      <c r="E36" s="85"/>
-      <c r="F36" s="85"/>
-      <c r="G36" s="85"/>
-      <c r="H36" s="85"/>
-      <c r="I36" s="85"/>
-      <c r="J36" s="76"/>
-      <c r="K36" s="76"/>
-      <c r="L36" s="76"/>
-      <c r="M36" s="76"/>
-      <c r="N36" s="76"/>
-      <c r="O36" s="76"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="79"/>
+      <c r="J36" s="49"/>
+      <c r="K36" s="49"/>
+      <c r="L36" s="49"/>
+      <c r="M36" s="49"/>
+      <c r="N36" s="49"/>
+      <c r="O36" s="49"/>
     </row>
     <row r="37" spans="1:15" ht="30" customHeight="1">
-      <c r="A37" s="87" t="s">
+      <c r="A37" s="54" t="s">
         <v>791</v>
       </c>
-      <c r="B37" s="85" t="s">
+      <c r="B37" s="79" t="s">
         <v>792</v>
       </c>
-      <c r="C37" s="85"/>
-      <c r="D37" s="85"/>
-      <c r="E37" s="85"/>
-      <c r="F37" s="85"/>
-      <c r="G37" s="85"/>
-      <c r="H37" s="85"/>
-      <c r="I37" s="85"/>
-      <c r="J37" s="76"/>
-      <c r="K37" s="76"/>
-      <c r="L37" s="76"/>
-      <c r="M37" s="76"/>
-      <c r="N37" s="76"/>
-      <c r="O37" s="76"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="79"/>
+      <c r="I37" s="79"/>
+      <c r="J37" s="49"/>
+      <c r="K37" s="49"/>
+      <c r="L37" s="49"/>
+      <c r="M37" s="49"/>
+      <c r="N37" s="49"/>
+      <c r="O37" s="49"/>
     </row>
     <row r="38" spans="1:15" ht="21" customHeight="1">
-      <c r="A38" s="76"/>
-      <c r="B38" s="76"/>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
-      <c r="I38" s="76"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="76"/>
-      <c r="L38" s="76"/>
-      <c r="M38" s="76"/>
-      <c r="N38" s="76"/>
-      <c r="O38" s="76"/>
+      <c r="A38" s="49"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="49"/>
+      <c r="J38" s="49"/>
+      <c r="K38" s="49"/>
+      <c r="L38" s="49"/>
+      <c r="M38" s="49"/>
+      <c r="N38" s="49"/>
+      <c r="O38" s="49"/>
     </row>
     <row r="39" spans="1:15" ht="21" customHeight="1">
-      <c r="A39" s="92" t="s">
+      <c r="A39" s="76" t="s">
         <v>793</v>
       </c>
-      <c r="B39" s="93"/>
-      <c r="C39" s="93"/>
-      <c r="D39" s="93"/>
-      <c r="E39" s="93"/>
-      <c r="F39" s="93"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="93"/>
-      <c r="I39" s="93"/>
-      <c r="J39" s="93"/>
-      <c r="K39" s="93"/>
-      <c r="L39" s="93"/>
-      <c r="M39" s="93"/>
-      <c r="N39" s="93"/>
-      <c r="O39" s="93"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
+      <c r="L39" s="77"/>
+      <c r="M39" s="77"/>
+      <c r="N39" s="77"/>
+      <c r="O39" s="77"/>
     </row>
     <row r="40" spans="1:15" ht="21" customHeight="1">
-      <c r="A40" s="95" t="s">
+      <c r="A40" s="58" t="s">
         <v>794</v>
       </c>
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="95" t="s">
+      <c r="C40" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="D40" s="95" t="s">
+      <c r="D40" s="58" t="s">
         <v>795</v>
       </c>
-      <c r="E40" s="95" t="s">
+      <c r="E40" s="58" t="s">
         <v>774</v>
       </c>
-      <c r="F40" s="95" t="s">
+      <c r="F40" s="58" t="s">
         <v>775</v>
       </c>
-      <c r="G40" s="95" t="s">
+      <c r="G40" s="58" t="s">
         <v>776</v>
       </c>
-      <c r="H40" s="95" t="s">
+      <c r="H40" s="58" t="s">
         <v>796</v>
       </c>
-      <c r="I40" s="95" t="s">
+      <c r="I40" s="58" t="s">
         <v>777</v>
       </c>
-      <c r="J40" s="95" t="s">
+      <c r="J40" s="58" t="s">
         <v>797</v>
       </c>
-      <c r="K40" s="95" t="s">
+      <c r="K40" s="58" t="s">
         <v>798</v>
       </c>
-      <c r="L40" s="95" t="s">
+      <c r="L40" s="58" t="s">
         <v>799</v>
       </c>
-      <c r="M40" s="95" t="s">
+      <c r="M40" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="N40" s="95" t="s">
+      <c r="N40" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="O40" s="95" t="s">
+      <c r="O40" s="58" t="s">
         <v>800</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="21" customHeight="1">
-      <c r="A41" s="73" t="s">
+      <c r="A41" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="B41" s="73" t="s">
+      <c r="B41" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="73" t="s">
+      <c r="C41" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="73" t="s">
+      <c r="D41" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="E41" s="73">
+      <c r="E41" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A41)</f>
         <v>12</v>
       </c>
-      <c r="F41" s="73">
+      <c r="F41" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A41,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>12</v>
       </c>
-      <c r="G41" s="73">
+      <c r="G41" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A41,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H41" s="73">
+      <c r="H41" s="46">
         <f t="shared" ref="H41:H55" si="6">E41-F41-G41</f>
         <v>0</v>
       </c>
-      <c r="I41" s="74">
+      <c r="I41" s="47">
         <f t="shared" ref="I41:I55" si="7">IFERROR(F41/E41,0)</f>
         <v>1</v>
       </c>
-      <c r="J41" s="73" t="str">
+      <c r="J41" s="46" t="str">
         <f t="shared" ref="J41:J55" si="8">IF(G41&gt;0,"FAIL",IF(H41&gt;0,"CHECK",IF(F41=E41,"PASS","NOT RUN")))</f>
         <v>PASS</v>
       </c>
-      <c r="K41" s="75" t="s">
+      <c r="K41" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="L41" s="75" t="s">
+      <c r="L41" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="M41" s="75" t="s">
+      <c r="M41" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="N41" s="73"/>
-      <c r="O41" s="73" t="s">
+      <c r="N41" s="46"/>
+      <c r="O41" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="21" customHeight="1">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="B42" s="73" t="s">
+      <c r="B42" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="73" t="s">
+      <c r="C42" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="73" t="s">
+      <c r="D42" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E42" s="73">
+      <c r="E42" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A42)</f>
         <v>15</v>
       </c>
-      <c r="F42" s="73">
+      <c r="F42" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A42,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>15</v>
       </c>
-      <c r="G42" s="73">
+      <c r="G42" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A42,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H42" s="73">
+      <c r="H42" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I42" s="74">
+      <c r="I42" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J42" s="73" t="str">
+      <c r="J42" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K42" s="75" t="s">
+      <c r="K42" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="L42" s="75" t="s">
+      <c r="L42" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="M42" s="75" t="s">
+      <c r="M42" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="N42" s="73"/>
-      <c r="O42" s="73" t="s">
+      <c r="N42" s="46"/>
+      <c r="O42" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="21" customHeight="1">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="B43" s="73" t="s">
+      <c r="B43" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="73" t="s">
+      <c r="C43" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="73" t="s">
+      <c r="D43" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E43" s="73">
+      <c r="E43" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A43)</f>
         <v>14</v>
       </c>
-      <c r="F43" s="73">
+      <c r="F43" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A43,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>14</v>
       </c>
-      <c r="G43" s="73">
+      <c r="G43" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A43,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H43" s="73">
+      <c r="H43" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I43" s="74">
+      <c r="I43" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J43" s="73" t="str">
+      <c r="J43" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K43" s="75" t="s">
+      <c r="K43" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="L43" s="75" t="s">
+      <c r="L43" s="48" t="s">
         <v>119</v>
       </c>
-      <c r="M43" s="75" t="s">
+      <c r="M43" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="N43" s="73"/>
-      <c r="O43" s="73" t="s">
+      <c r="N43" s="46"/>
+      <c r="O43" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="21" customHeight="1">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="B44" s="73" t="s">
+      <c r="B44" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="73" t="s">
+      <c r="C44" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="73" t="s">
+      <c r="D44" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E44" s="73">
+      <c r="E44" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A44)</f>
         <v>10</v>
       </c>
-      <c r="F44" s="73">
+      <c r="F44" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A44,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>10</v>
       </c>
-      <c r="G44" s="73">
+      <c r="G44" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A44,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H44" s="73">
+      <c r="H44" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I44" s="74">
+      <c r="I44" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J44" s="73" t="str">
+      <c r="J44" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K44" s="75" t="s">
+      <c r="K44" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="L44" s="75" t="s">
+      <c r="L44" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="M44" s="75" t="s">
+      <c r="M44" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="N44" s="73"/>
-      <c r="O44" s="73" t="s">
+      <c r="N44" s="46"/>
+      <c r="O44" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="21" customHeight="1">
-      <c r="A45" s="73" t="s">
+      <c r="A45" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="B45" s="73" t="s">
+      <c r="B45" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C45" s="73" t="s">
+      <c r="C45" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="73" t="s">
+      <c r="D45" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="73">
+      <c r="E45" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A45)</f>
         <v>14</v>
       </c>
-      <c r="F45" s="73">
+      <c r="F45" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A45,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>14</v>
       </c>
-      <c r="G45" s="73">
+      <c r="G45" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A45,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H45" s="73">
+      <c r="H45" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I45" s="74">
+      <c r="I45" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J45" s="73" t="str">
+      <c r="J45" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K45" s="75" t="s">
+      <c r="K45" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="L45" s="75" t="s">
+      <c r="L45" s="48" t="s">
         <v>121</v>
       </c>
-      <c r="M45" s="75" t="s">
+      <c r="M45" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="N45" s="73"/>
-      <c r="O45" s="73" t="s">
+      <c r="N45" s="46"/>
+      <c r="O45" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="21" customHeight="1">
-      <c r="A46" s="73" t="s">
+      <c r="A46" s="46" t="s">
         <v>106</v>
       </c>
-      <c r="B46" s="73" t="s">
+      <c r="B46" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C46" s="73" t="s">
+      <c r="C46" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="73" t="s">
+      <c r="D46" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E46" s="73">
+      <c r="E46" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A46)</f>
         <v>16</v>
       </c>
-      <c r="F46" s="73">
+      <c r="F46" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A46,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>16</v>
       </c>
-      <c r="G46" s="73">
+      <c r="G46" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A46,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H46" s="73">
+      <c r="H46" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I46" s="74">
+      <c r="I46" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J46" s="73" t="str">
+      <c r="J46" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K46" s="75" t="s">
+      <c r="K46" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="L46" s="75" t="s">
+      <c r="L46" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="M46" s="75" t="s">
+      <c r="M46" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="N46" s="73"/>
-      <c r="O46" s="73" t="s">
+      <c r="N46" s="46"/>
+      <c r="O46" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="21" customHeight="1">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="73" t="s">
+      <c r="B47" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C47" s="73" t="s">
+      <c r="C47" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="73" t="s">
+      <c r="D47" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="E47" s="73">
+      <c r="E47" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A47)</f>
         <v>13</v>
       </c>
-      <c r="F47" s="73">
+      <c r="F47" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A47,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>13</v>
       </c>
-      <c r="G47" s="73">
+      <c r="G47" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A47,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H47" s="73">
+      <c r="H47" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I47" s="74">
+      <c r="I47" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J47" s="73" t="str">
+      <c r="J47" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K47" s="75" t="s">
+      <c r="K47" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="L47" s="75" t="s">
+      <c r="L47" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="M47" s="75" t="s">
+      <c r="M47" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="N47" s="73"/>
-      <c r="O47" s="73" t="s">
+      <c r="N47" s="46"/>
+      <c r="O47" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="21" customHeight="1">
-      <c r="A48" s="73" t="s">
+      <c r="A48" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="B48" s="73" t="s">
+      <c r="B48" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="73" t="s">
+      <c r="C48" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D48" s="73" t="s">
+      <c r="D48" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E48" s="73">
+      <c r="E48" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A48)</f>
         <v>16</v>
       </c>
-      <c r="F48" s="73">
+      <c r="F48" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A48,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>16</v>
       </c>
-      <c r="G48" s="73">
+      <c r="G48" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A48,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H48" s="73">
+      <c r="H48" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I48" s="74">
+      <c r="I48" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J48" s="73" t="str">
+      <c r="J48" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K48" s="75" t="s">
+      <c r="K48" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="L48" s="75" t="s">
+      <c r="L48" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="M48" s="75" t="s">
+      <c r="M48" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="N48" s="73"/>
-      <c r="O48" s="73" t="s">
+      <c r="N48" s="46"/>
+      <c r="O48" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="21" customHeight="1">
-      <c r="A49" s="73" t="s">
+      <c r="A49" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="B49" s="73" t="s">
+      <c r="B49" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="73" t="s">
+      <c r="C49" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="73" t="s">
+      <c r="D49" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="E49" s="73">
+      <c r="E49" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A49)</f>
         <v>14</v>
       </c>
-      <c r="F49" s="73">
+      <c r="F49" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A49,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>14</v>
       </c>
-      <c r="G49" s="73">
+      <c r="G49" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A49,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H49" s="73">
+      <c r="H49" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I49" s="74">
+      <c r="I49" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J49" s="73" t="str">
+      <c r="J49" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K49" s="75" t="s">
+      <c r="K49" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="L49" s="75" t="s">
+      <c r="L49" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="M49" s="75" t="s">
+      <c r="M49" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="N49" s="73"/>
-      <c r="O49" s="73" t="s">
+      <c r="N49" s="46"/>
+      <c r="O49" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="21" customHeight="1">
-      <c r="A50" s="73" t="s">
+      <c r="A50" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="73" t="s">
+      <c r="B50" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="73" t="s">
+      <c r="C50" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="73" t="s">
+      <c r="D50" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E50" s="73">
+      <c r="E50" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A50)</f>
         <v>13</v>
       </c>
-      <c r="F50" s="73">
+      <c r="F50" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A50,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>13</v>
       </c>
-      <c r="G50" s="73">
+      <c r="G50" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A50,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H50" s="73">
+      <c r="H50" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I50" s="74">
+      <c r="I50" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J50" s="73" t="str">
+      <c r="J50" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K50" s="75" t="s">
+      <c r="K50" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="L50" s="75" t="s">
+      <c r="L50" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="M50" s="75" t="s">
+      <c r="M50" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="N50" s="73"/>
-      <c r="O50" s="73" t="s">
+      <c r="N50" s="46"/>
+      <c r="O50" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="21" customHeight="1">
-      <c r="A51" s="73" t="s">
+      <c r="A51" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="B51" s="73" t="s">
+      <c r="B51" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C51" s="73" t="s">
+      <c r="C51" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="73" t="s">
+      <c r="D51" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="E51" s="73">
+      <c r="E51" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A51)</f>
         <v>13</v>
       </c>
-      <c r="F51" s="73">
+      <c r="F51" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A51,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>13</v>
       </c>
-      <c r="G51" s="73">
+      <c r="G51" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A51,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H51" s="73">
+      <c r="H51" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I51" s="74">
+      <c r="I51" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J51" s="73" t="str">
+      <c r="J51" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K51" s="75" t="s">
+      <c r="K51" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="L51" s="75" t="s">
+      <c r="L51" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="M51" s="75" t="s">
+      <c r="M51" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="N51" s="73"/>
-      <c r="O51" s="73" t="s">
+      <c r="N51" s="46"/>
+      <c r="O51" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="21" customHeight="1">
-      <c r="A52" s="73" t="s">
+      <c r="A52" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="B52" s="73" t="s">
+      <c r="B52" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C52" s="73" t="s">
+      <c r="C52" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D52" s="73" t="s">
+      <c r="D52" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E52" s="73">
+      <c r="E52" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A52)</f>
         <v>18</v>
       </c>
-      <c r="F52" s="73">
+      <c r="F52" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A52,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>18</v>
       </c>
-      <c r="G52" s="73">
+      <c r="G52" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A52,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H52" s="73">
+      <c r="H52" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I52" s="74">
+      <c r="I52" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J52" s="73" t="str">
+      <c r="J52" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K52" s="75" t="s">
+      <c r="K52" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="L52" s="75" t="s">
+      <c r="L52" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="M52" s="75" t="s">
+      <c r="M52" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="N52" s="73"/>
-      <c r="O52" s="73" t="s">
+      <c r="N52" s="46"/>
+      <c r="O52" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="21" customHeight="1">
-      <c r="A53" s="73" t="s">
+      <c r="A53" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="B53" s="73" t="s">
+      <c r="B53" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C53" s="73" t="s">
+      <c r="C53" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="D53" s="73" t="s">
+      <c r="D53" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="E53" s="73">
+      <c r="E53" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A53)</f>
         <v>15</v>
       </c>
-      <c r="F53" s="73">
+      <c r="F53" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A53,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>15</v>
       </c>
-      <c r="G53" s="73">
+      <c r="G53" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A53,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H53" s="73">
+      <c r="H53" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I53" s="74">
+      <c r="I53" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J53" s="73" t="str">
+      <c r="J53" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K53" s="75" t="s">
+      <c r="K53" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="L53" s="75" t="s">
+      <c r="L53" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="M53" s="75" t="s">
+      <c r="M53" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="N53" s="73"/>
-      <c r="O53" s="73" t="s">
+      <c r="N53" s="46"/>
+      <c r="O53" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="21" customHeight="1">
-      <c r="A54" s="73" t="s">
+      <c r="A54" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="B54" s="73" t="s">
+      <c r="B54" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C54" s="73" t="s">
+      <c r="C54" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="D54" s="73" t="s">
+      <c r="D54" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E54" s="73">
+      <c r="E54" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A54)</f>
         <v>19</v>
       </c>
-      <c r="F54" s="73">
+      <c r="F54" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A54,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>19</v>
       </c>
-      <c r="G54" s="73">
+      <c r="G54" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A54,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H54" s="73">
+      <c r="H54" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I54" s="74">
+      <c r="I54" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J54" s="73" t="str">
+      <c r="J54" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K54" s="75" t="s">
+      <c r="K54" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="L54" s="75" t="s">
+      <c r="L54" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="M54" s="75" t="s">
+      <c r="M54" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="N54" s="73"/>
-      <c r="O54" s="73" t="s">
+      <c r="N54" s="46"/>
+      <c r="O54" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="21" customHeight="1">
-      <c r="A55" s="73" t="s">
+      <c r="A55" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="B55" s="73" t="s">
+      <c r="B55" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C55" s="73" t="s">
+      <c r="C55" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="D55" s="73" t="s">
+      <c r="D55" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="E55" s="73">
+      <c r="E55" s="46">
         <f>COUNTIF([1]inZOI_Steps!$A$5:$A$221,A55)</f>
         <v>15</v>
       </c>
-      <c r="F55" s="73">
+      <c r="F55" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A55,[1]inZOI_Steps!$F$5:$F$221,"PASS")</f>
         <v>15</v>
       </c>
-      <c r="G55" s="73">
+      <c r="G55" s="46">
         <f>COUNTIFS([1]inZOI_Steps!$A$5:$A$221,A55,[1]inZOI_Steps!$F$5:$F$221,"FAIL")</f>
         <v>0</v>
       </c>
-      <c r="H55" s="73">
+      <c r="H55" s="46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I55" s="74">
+      <c r="I55" s="47">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J55" s="73" t="str">
+      <c r="J55" s="46" t="str">
         <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
-      <c r="K55" s="75" t="s">
+      <c r="K55" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="L55" s="75" t="s">
+      <c r="L55" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="M55" s="75" t="s">
+      <c r="M55" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="N55" s="73"/>
-      <c r="O55" s="73" t="s">
+      <c r="N55" s="46"/>
+      <c r="O55" s="46" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="21" customHeight="1">
-      <c r="A56" s="76"/>
-      <c r="B56" s="76"/>
-      <c r="C56" s="76"/>
-      <c r="D56" s="76"/>
-      <c r="E56" s="76"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="76"/>
-      <c r="H56" s="76"/>
-      <c r="I56" s="76"/>
-      <c r="J56" s="76"/>
-      <c r="K56" s="76"/>
-      <c r="L56" s="76"/>
-      <c r="M56" s="76"/>
-      <c r="N56" s="76"/>
-      <c r="O56" s="76"/>
+      <c r="A56" s="49"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="49"/>
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="49"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="49"/>
+      <c r="L56" s="49"/>
+      <c r="M56" s="49"/>
+      <c r="N56" s="49"/>
+      <c r="O56" s="49"/>
     </row>
     <row r="57" spans="1:15" ht="21" customHeight="1">
-      <c r="A57" s="76"/>
-      <c r="B57" s="76"/>
-      <c r="C57" s="76"/>
-      <c r="D57" s="76"/>
-      <c r="E57" s="76"/>
-      <c r="F57" s="76"/>
-      <c r="G57" s="76"/>
-      <c r="H57" s="76"/>
-      <c r="I57" s="76"/>
-      <c r="J57" s="76"/>
-      <c r="K57" s="76"/>
-      <c r="L57" s="76"/>
-      <c r="M57" s="76"/>
-      <c r="N57" s="76"/>
-      <c r="O57" s="76"/>
+      <c r="A57" s="49"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="49"/>
+      <c r="J57" s="49"/>
+      <c r="K57" s="49"/>
+      <c r="L57" s="49"/>
+      <c r="M57" s="49"/>
+      <c r="N57" s="49"/>
+      <c r="O57" s="49"/>
     </row>
     <row r="58" spans="1:15" ht="21" customHeight="1">
-      <c r="A58" s="77" t="s">
+      <c r="A58" s="78" t="s">
         <v>801</v>
       </c>
-      <c r="B58" s="77"/>
-      <c r="C58" s="77"/>
-      <c r="D58" s="77"/>
-      <c r="E58" s="77"/>
-      <c r="F58" s="77"/>
-      <c r="G58" s="77"/>
-      <c r="H58" s="77"/>
-      <c r="I58" s="77"/>
-      <c r="J58" s="77"/>
-      <c r="K58" s="77"/>
-      <c r="L58" s="77"/>
-      <c r="M58" s="77"/>
-      <c r="N58" s="77"/>
-      <c r="O58" s="77"/>
+      <c r="B58" s="78"/>
+      <c r="C58" s="78"/>
+      <c r="D58" s="78"/>
+      <c r="E58" s="78"/>
+      <c r="F58" s="78"/>
+      <c r="G58" s="78"/>
+      <c r="H58" s="78"/>
+      <c r="I58" s="78"/>
+      <c r="J58" s="78"/>
+      <c r="K58" s="78"/>
+      <c r="L58" s="78"/>
+      <c r="M58" s="78"/>
+      <c r="N58" s="78"/>
+      <c r="O58" s="78"/>
     </row>
     <row r="59" spans="1:15" ht="21" customHeight="1">
-      <c r="A59" s="76"/>
-      <c r="B59" s="76"/>
-      <c r="C59" s="76"/>
-      <c r="D59" s="76"/>
-      <c r="E59" s="76"/>
-      <c r="F59" s="76"/>
-      <c r="G59" s="76"/>
-      <c r="H59" s="76"/>
-      <c r="I59" s="76"/>
-      <c r="J59" s="76"/>
-      <c r="K59" s="76"/>
-      <c r="L59" s="76"/>
-      <c r="M59" s="76"/>
-      <c r="N59" s="76"/>
-      <c r="O59" s="76"/>
+      <c r="A59" s="49"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="49"/>
+      <c r="I59" s="49"/>
+      <c r="J59" s="49"/>
+      <c r="K59" s="49"/>
+      <c r="L59" s="49"/>
+      <c r="M59" s="49"/>
+      <c r="N59" s="49"/>
+      <c r="O59" s="49"/>
     </row>
     <row r="60" spans="1:15" ht="21" customHeight="1">
-      <c r="A60" s="76"/>
-      <c r="B60" s="76"/>
-      <c r="C60" s="76"/>
-      <c r="D60" s="76"/>
-      <c r="E60" s="76"/>
-      <c r="F60" s="76"/>
-      <c r="G60" s="76"/>
-      <c r="H60" s="76"/>
-      <c r="I60" s="76"/>
-      <c r="J60" s="76"/>
-      <c r="K60" s="76"/>
-      <c r="L60" s="76"/>
-      <c r="M60" s="76"/>
-      <c r="N60" s="76"/>
-      <c r="O60" s="76"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="49"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="49"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="49"/>
+      <c r="J60" s="49"/>
+      <c r="K60" s="49"/>
+      <c r="L60" s="49"/>
+      <c r="M60" s="49"/>
+      <c r="N60" s="49"/>
+      <c r="O60" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="D5:F6"/>
-    <mergeCell ref="G5:I6"/>
-    <mergeCell ref="J5:L6"/>
-    <mergeCell ref="M5:O6"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="A58:O58"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="J28:O28"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B37:I37"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="I14:O14"/>
     <mergeCell ref="A9:C9"/>
@@ -23268,15 +23178,23 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="J12:L12"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="A39:O39"/>
-    <mergeCell ref="A58:O58"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="J28:O28"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="D5:F6"/>
+    <mergeCell ref="G5:I6"/>
+    <mergeCell ref="J5:L6"/>
+    <mergeCell ref="M5:O6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="M4:O4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D30:D32">
@@ -23343,10 +23261,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J41:J55">
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>J41="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>J41="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
